--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -7,7 +7,9 @@
     <sheet name="멤버 리스트" sheetId="3" r:id="rId3"/>
     <sheet name="소식·일정" sheetId="4" r:id="rId4"/>
     <sheet name="팬덤레벨" sheetId="5" r:id="rId5"/>
-    <sheet name="덕력관리" sheetId="6" r:id="rId6"/>
+    <sheet name="보상·레벨업 현황" sheetId="6" r:id="rId6"/>
+    <sheet name="덕력관리" sheetId="7" r:id="rId7"/>
+    <sheet name="서포트 관리" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -19088,6 +19090,1362 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Depth1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Depth2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Depth3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면명</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트 항목</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트 내용</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예상결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사이드바 아티스트 &gt; 보상·레벨업 현황 클릭 → /artists/fandom/status 진입</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 현황 페이지 진입</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">브레드크럼·타이틀·부제</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'홈&gt;아티스트&gt;팬덤레벨&gt;보상·레벨업 현황' + 타이틀 '보상·레벨업 현황' + 부제 '전체 시즌 통합 현황'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹 필터 드롭다운</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹(전체) + 활성 그룹(V01D·iKON·MADEIN·CELEBUS·언더라이트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시즌 필터 드롭다운</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시즌(전체) + 전체 시즌 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨 필터 드롭다운</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨(전체) + 전체 시즌 통합 레벨 목록(정렬)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기간 From~To(날짜) 입력</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달성·지급 일시 기준 기간 필터(YYYY.MM.DD 비교)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹+시즌+레벨+기간 조합</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AND 조합 필터 결과 노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[초기화] 클릭</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모든 필터·검색어·페이지 초기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터 변경 시</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지 1로 리셋</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">섹션 전환</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">섹션 토글 2종</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력 / 디지털 굿즈(BIVE) 지급 연계</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">섹션 전환</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">섹션 전환</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해당 섹션 테이블로 전환 + 페이지 1로 리셋</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">섹션 전환</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닉네임 검색 노출 조건</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닉네임 검색은 BIVE 지급 연계 섹션에서만 노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력 컬럼</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹/시즌/레벨/달성 일시/연결 보상</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조회 범위</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 시즌 통합(모든 시즌 레벨업 이력 합산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정렬</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달성 일시 내림차순(최신순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹·시즌 링크 클릭</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해당 시즌 상세(/artists/fandom/{id})로 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연결 보상 표기</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디지털 굿즈 캠페인명 / 래플·서포트 예고 문구 / '-'(미설정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨별 회원 수 컬럼 없음</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 현황은 레벨별 회원 수 미표시(시즌 상세 EVT-205에서만 시즌 전체 기여 회원 표시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지네이션</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지당 10건</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업 이력</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 0건 / 검색 0건</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'조회된 내역이 없습니다.' / '검색 결과가 없습니다.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 연계</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 컬럼</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹/시즌/레벨/회원/캠페인/지급 상태/일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 연계</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 상태 배지</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기(회색)/민팅중(파랑)/완료(에메랄드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 연계</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필터</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닉네임 검색</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원 닉네임 부분 일치 검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 연계</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정렬</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 일시 내림차순(최신순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 연계</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디지털 굿즈만 대상</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래플·서포트 예고는 지급 대상 아님 — 표시되지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 연계</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지네이션</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지당 10건</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 연계</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 0건 / 검색 0건</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'조회된 내역이 없습니다.' / '검색 결과가 없습니다.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">범위</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통합 vs 시즌 구분</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본 화면=전체 시즌 통합 조회(필터 보유). 시즌 상세 현황 탭(EVT-205)=특정 시즌 1건(필터 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현황 공통</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">범위</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">읽기 전용</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 섹션 조회 전용(편집·상태 변경 액션 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 지급 상태 실시간 반영</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대기/민팅중/완료 상태는 BIVE 영역 민팅 처리 상태가 실시간 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_FRS_0031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨업</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상·레벨업 현황</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">레벨 달성 → 현황 반영</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팬덤 레벨 달성(앱) 시 레벨업 이력·BIVE 지급 연계에 자동 기록</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -22496,4 +23854,3692 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:H88"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Depth1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Depth2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Depth3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화면명</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트 항목</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테스트 내용</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예상결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사이드바 아티스트 &gt; 서포트 관리 클릭 → /artists/support 진입</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리 리스트 진입</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">브레드크럼·타이틀·헤더 버튼</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'홈&gt;아티스트&gt;서포트 관리' + 타이틀 + [변동 내역]·[이벤트 생성]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대시보드</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태별 카드 8종</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임시저장/모집대기/모집중/달성/집행중/완료/미달성종료/집행취소 카드 + 건수, 라이프사이클 순</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대시보드</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카드 색상</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태별 배지 색상 정합(모집대기=하늘·모집중=초록·달성=남색·집행중=주황·완료=진회색·미달성종료/집행취소=분홍)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대시보드</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 카드 클릭 → 재클릭</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해당 상태 단일 필터 → 재클릭 시 전체 해제(토글)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색·필터</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 필터 드롭다운</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 + 8상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색·필터</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹 필터 드롭다운</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전체 + 활성 아티스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색·필터</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이벤트명 검색 + [초기화]</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부분 일치 검색, 초기화 시 리셋</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블 컬럼</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태/이벤트명/그룹/기간/응원자 수/누적 응원/달성률</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달성률 강조</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100% 이상 시 강조(인디고 굵게)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정렬</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마감 임박순→생성 최신순, 종료군(완료·미달성종료·집행취소)은 하단(고정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">행 클릭</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보 탭)로 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지네이션</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지당 10건, 필터 변경 시 1페이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loading / 전체 0건 / 검색 0건</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skeleton / '생성된 서포트 이벤트가 없습니다.' / '검색 결과가 없습니다.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 리스트</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목록 조회 실패</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 안내 + [재시도]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변동 내역</t>
+        </is>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원·반환 변동 내역</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달확인</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트에서 [변동 내역] 클릭</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변동 내역 페이지(/artists/support/history) 진입</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변동 내역</t>
+        </is>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원·반환 변동 내역</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원/반환 탭</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원·반환 2탭 + 각 건수 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변동 내역</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색·필터</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원·반환 변동 내역</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이벤트·그룹·기간·닉네임 필터 + [초기화]</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AND 조합 필터, 초기화는 탭 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변동 내역</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원·반환 변동 내역</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블 컬럼·색상</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원/이벤트명/그룹/변동 내용(응원 +emerald, 반환 −rose)/일시, 회차별 1행</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변동 내역</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원·반환 변동 내역</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정렬·페이지네이션</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">최신순, 페이지당 10건</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변동 내역</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원·반환 변동 내역</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 0건</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'검색 결과가 없습니다.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달확인</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트에서 [이벤트 생성] 클릭</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 페이지(/new) 진입</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본 정보</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이벤트명·설명 다국어</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국어/영어/일본어(이벤트명 50자·설명 500자), 미입력 칸 빨간 점</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상·목표</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹·목표 응원량</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그룹 드롭다운(활성) + 목표 응원량(1 이상 정수, 덕력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일정</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시작·마감일시</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">datetime(KST), 마감 &gt; 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대표 이미지</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대표 이미지 업로드</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 필수, 16:9 크롭, JPG/PNG/WEBP, 5MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홈 카드</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">홈 카드 이미지·타이틀·서브타이틀</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카드 이미지(1:1 필수)·카드 타이틀 다국어(30자 필수)·서브타이틀(50자 선택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유의사항</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">유의사항 다국어(선택)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">한국어/영어/일본어 각 500자, 앱 상세 노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이벤트명/설명 일부 언어 미입력</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[생성하기] 비활성 + 미입력 칸 빨간 점</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목표 응원량 0·음수</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'목표 응원량은 1 이상이어야 합니다.' + 비활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마감 ≤ 시작</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'마감일시는 시작일시보다 늦어야 합니다.' + 비활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대표/홈카드 이미지 미업로드</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[생성하기] 비활성 + 누락 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이미지 형식·용량 위반</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'허용되지 않는 파일입니다.' 거부</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">카드 타이틀 일부 언어 미입력</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[생성하기] 비활성 + 빨간 점</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검증</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수값 전체 충족</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[생성하기] 활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[임시저장](이벤트명 한국어만)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임시저장 상태 저장 + '임시저장되었습니다' 토스트 + 리스트 복귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[생성하기](필수값 전체)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임시저장 상태 저장 + '서포트 이벤트가 생성되었습니다' 토스트 + 리스트 복귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 생성</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">백오피스 액션</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 활동 로그</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'서포트 이벤트 {이벤트명}을(를) 생성했습니다 (그룹·기간)' 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취소 모달</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 취소 확인</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">입력값 있는 상태 [취소]</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'작성을 취소할까요?' 모달 → [계속 작성] 유지 / [나가기] 폐기·리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">취소 모달</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생성 취소 확인</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">입력값 없는 상태 [취소]</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">즉시 리스트 복귀(모달 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤더</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달확인</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트 행 클릭 → 상세 진입</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본정보 탭 진입, 헤더(이벤트명·그룹·상태 배지·기간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤더</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">탭 메뉴 3종</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본정보 / 응원자 내역 / 결과물·반환</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤더</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태별 헤더 액션 버튼</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임시저장=[게시][삭제] / 모집대기=[삭제] / 모집중=[강제 종료] / 달성=[집행 시작][집행 취소] / 집행중=[결과물 등록·완료][집행 취소] / 완료·미달성종료·집행취소=없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통계</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통계 카드</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모집중 이상=응원자 수·누적 응원·평균 응원량·달성률 노출 / 임시저장·모집대기=미노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기본 정보</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">조회 정보</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이벤트명·설명·그룹·목표·기간·대표이미지(16:9)·홈카드(1:1)·유의사항 다국어</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수정</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태별 수정 범위</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임시저장=전 항목(그룹 제외) / 모집대기=목표·기간 포함 / 모집중=이름·설명·이미지·홈카드·유의사항만(목표·기간 잠금) / 달성 이상=읽기 전용([수정] 미노출)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수정</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[수정]→[저장]</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경 시 활성, 저장 후 '저장되었습니다' 토스트 + 활동 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수정</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수정 중 탭 전환·[취소](변경 있음)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'저장하지 않은 변경이 있습니다. 이동할까요?' 모달</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상세</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수정</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경 없을 때 [저장]</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게시 모달</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게시 확인</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임시저장에서 [게시]→[게시] (필수값 충족)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'게시할까요?' 모달 → 모집대기 전환(시작일시 도달 시 자동 모집중) + 토스트 + 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게시 모달</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게시 확인</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수값 미입력 게시 시도</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'필수 항목을 모두 입력해야 게시할 수 있습니다.' 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 모달</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 확인</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모집중에서 [강제 종료] 클릭</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'강제 종료할까요? 응원 회원 N명에게 N 덕력 전액 반환 / 되돌릴 수 없습니다' 모달({N} 스냅샷)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 모달</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 확인</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[강제 종료] 확정</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미달성종료 전환 + 응원 회원 전원 전액 자동 반환(사유 강제 종료) + 토스트 + 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 모달</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 확인</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료는 모집중 전용</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달성·집행중에는 [강제 종료] 미노출(집행 취소 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행 시작 모달</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행 시작 확인</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달성에서 [집행 시작]→확정</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행중 전환 + 응원 덕력 집행 비용 확정(반환 대상 아님) + 토스트 + 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행 취소 모달</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행 취소 확인</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달성·집행중에서 [집행 취소]→확정</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행취소 전환 + 응원 회원 전원 전액 자동 반환(사유 집행 취소) + 토스트 + 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물 완료 모달</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물 등록·완료</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과 메시지 일부 언어·사진 0장</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료 차단 — '결과 메시지 3언어 입력' / '사진·영상 최소 1장'</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물 완료 모달</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물 등록·완료</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행중에서 결과 메시지(3언어)+사진 입력 후 [등록하고 완료]</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">완료 전환 + 결과물 앱 공개 + 응원 회원 알림 발송 + 토스트 + 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제 모달</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이벤트 삭제 확인</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">임시저장·모집대기에서 [삭제]→[삭제]</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'복구할 수 없습니다' 모달 → 삭제 + 리스트 복귀 + 토스트 + 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제 모달</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이벤트 삭제 확인</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모집중 이상 삭제 불가</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[삭제] 미노출(강제 종료·집행 취소 사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경합</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달 진입 후 상태 변경(경합)</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'이미 상태가 변경되었습니다. 새로고침 후 다시 시도하세요.' + 최신 상태 갱신</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자동 전환</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서버 자동 전환</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모집대기→모집중(시작일시)·모집중→달성(누적≥목표)·모집중→미달성종료(마감+미달성, 전액 반환)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 전환</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 정책</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료·집행 취소·미달성종료 = 응원 회원 전원 전액 즉시 자동 반환(보유 덕력 복구). 정상 완료는 반환 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(응원자 내역)</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달확인</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[응원자 내역] 탭 클릭</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역 탭 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(응원자 내역)</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요약 카드</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 수·총 응원 횟수·누적 응원</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(응원자 내역)</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블 컬럼·정렬</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닉네임/누적 응원량/응원 횟수(2회↑ 강조)/최초 응원/최근 응원/반환 여부, 누적 응원량 내림차순</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(응원자 내역)</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지네이션</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">페이지당 10건</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">테이블</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(응원자 내역)</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원 0건 / Error</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'아직 응원한 회원이 없습니다.' / '데이터를 불러오지 못했습니다.'+[재시도]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회차 모달</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원 상세(회차별)</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달확인</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원 행 클릭</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'{닉네임} 응원 내역' 모달, 회차/응원량/응원 시점</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회차 모달</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원 상세(회차별)</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회차 정렬·페이지네이션</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원 시점 오름차순, 10건/페이지, 회차 번호 전체 기준 연속(2페이지 첫 행=11회차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회차 모달</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원 상세(회차별)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누적(전체) 합계</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">현재 페이지 합이 아닌 전체 누적 응원량 고정 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원자 내역</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회차 모달</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원 상세(회차별)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 표기</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 상태일 때 '전액 반환 완료(시점)' 표기</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환</t>
+        </is>
+      </c>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(결과물·반환)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달확인</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[결과물·반환] 탭 클릭</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환 탭 전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(결과물·반환)</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태별 결과물 영역</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행중=입력 가능 / 완료=읽기 전용 / 임시저장·모집중·달성=안내(입력 비활성) / 미달성종료·집행취소=미노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(결과물·반환)</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과 메시지 다국어·사진/영상</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과 메시지 한국어/영어/일본어 각 200자 + 사진·영상 최대 10장</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 현황</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(결과물·반환)</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 요약(미달성종료·집행취소)</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 사유·방식(서버 자동·즉시 전액)·반환율 100%·반환 대상·반환 총 덕력·완료 시점</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 현황</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(결과물·반환)</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원별 반환 내역</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">닉네임/반환 덕력(강조)/원 응원 횟수/반환 시점/반환 완료 배지, 반환 덕력 내림차순</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 현황</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(결과물·반환)</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정상 진행·완료</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'반환된 응원이 없습니다. (정상 집행·완료 이벤트는 반환 없음)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">결과물·반환</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환 현황</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(결과물·반환)</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영자 수동 반환 없음</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환은 서버 자동만(운영자 반환 버튼 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0080</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노출</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 서포트 이벤트(DUK)</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">게시→모집대기→모집중(시작일시) → 앱</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시작일시 도달 시 앱 서포트 이벤트 노출·응원 시작(모집대기는 미노출)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0081</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응원</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 서포트 이벤트(DUK)</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 응원 → BO</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">즉시 누적 응원·응원자 내역에 반영(보유 덕력 1:1 차감, 랭킹·팬덤레벨 무가산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달성</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 서포트 이벤트(DUK)</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">누적 ≥ 목표 → 앱</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목표 달성·집행 대기 표시, 응원 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행/완료</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 서포트 이벤트(DUK)</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">집행 시작·결과물 완료 → 앱</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 진행중 표시, 완료 시 결과물 갤러리 공개 + 결과물 알림 발송</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반환</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 서포트 이벤트(DUK)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료·집행 취소·미달성종료 → 앱</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전액 반환·보유 덕력 즉시 복구 + 반환 알림</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">초과 응원</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 서포트 이벤트(DUK)</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">목표 근접 시 초과 응원</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남은 목표량까지만 차감, 초과분 보유 덕력 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">권한</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 상세(기본정보)</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쓰기/삭제 권한 없음·외부 아티스트</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쓰기 없음=수정·상태 전환·삭제 미노출 / 삭제 없음=[삭제]만 미노출 / 외부 아티스트=자신 그룹만 조회, 쓰기 미노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_SUP_0087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서포트 관리</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">예외</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스냅샷</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 확인</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">강제 종료 {N} 스냅샷</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">모달 표기 N은 진입 시점 누적(모집중은 응원 계속 가능) — 실제 반환은 전이 시점 전액(반환율 100%)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -27593,7 +27593,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">레벨/레벨업 목표 덕력/권장값/달성 여부/달성 일시</t>
+          <t xml:space="preserve">레벨/레벨업 목표 덕력/권장값/레벨업 여부/레벨업 일시</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27761,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">목표 덕력 입력 활성(달성 레벨 비활성), [권장 곡선 적용]·[저장]·[취소] 노출</t>
+          <t xml:space="preserve">목표 덕력 입력 활성(현재 레벨 이하 비활성), [권장 곡선 적용]·[저장]·[취소] 노출</t>
         </is>
       </c>
     </row>
@@ -27803,7 +27803,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미달성 신규 레벨 추가(최대 10), 권장값 기본 채움</t>
+          <t xml:space="preserve">현재 레벨 초과 신규 레벨 추가(최대 10), 권장값 기본 채움</t>
         </is>
       </c>
     </row>
@@ -27882,7 +27882,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미달성 레벨 [X] 삭제</t>
+          <t xml:space="preserve">현재 레벨 초과 레벨 [X] 삭제</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -27924,12 +27924,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달성 레벨 삭제·수정 시도</t>
+          <t xml:space="preserve">현재 레벨 이하 삭제·수정 시도</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비활성 + '이미 달성된 레벨은 수정·삭제할 수 없습니다.'</t>
+          <t xml:space="preserve">비활성 + '현재 레벨 이하는 수정·삭제할 수 없습니다.'</t>
         </is>
       </c>
     </row>
@@ -28223,7 +28223,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미달성 레벨 추가 가능, 신규 레벨 보상은 추가 이후 달성 시점부터 적용(소급 없음)</t>
+          <t xml:space="preserve">현재 레벨 초과 레벨 추가 가능, 신규 레벨 보상은 추가 이후 진입 시점부터 적용(소급 없음)</t>
         </is>
       </c>
     </row>
@@ -28349,7 +28349,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">선택 레벨의 보상만 표시 + 달성/미달성 배지</t>
+          <t xml:space="preserve">선택 레벨의 보상만 표시 + 레벨업 완료/미완료 배지</t>
         </is>
       </c>
     </row>
@@ -28596,7 +28596,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[수정] → [보상 추가](미달성 레벨)</t>
+          <t xml:space="preserve">[수정] → [보상 추가](현재 레벨 초과 레벨)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -28974,12 +28974,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달성 레벨 보상 수정·삭제 시도</t>
+          <t xml:space="preserve">현재 레벨 이하 보상 수정·삭제 시도</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비활성 + '이미 달성된 레벨의 보상은 수정·삭제할 수 없습니다.'</t>
+          <t xml:space="preserve">비활성 + '현재 레벨 이하의 보상은 수정·삭제할 수 없습니다.'</t>
         </is>
       </c>
     </row>
@@ -29231,7 +29231,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">레벨/달성 일시/연결 보상, 달성 일시 내림차순</t>
+          <t xml:space="preserve">레벨/레벨업 일시/연결 보상, 레벨업 일시 내림차순</t>
         </is>
       </c>
     </row>
@@ -30239,7 +30239,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경된 레벨 보상 앱 반영(달성 레벨은 소급 없음)</t>
+          <t xml:space="preserve">변경된 레벨 보상 앱 반영(현재 레벨 이하는 소급 없음)</t>
         </is>
       </c>
     </row>
@@ -30587,7 +30587,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달성·지급 일시 기준 기간 필터(YYYY.MM.DD 비교)</t>
+          <t xml:space="preserve">레벨업·지급 일시 기준 기간 필터(YYYY.MM.DD 비교)</t>
         </is>
       </c>
     </row>
@@ -30881,7 +30881,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그룹/시즌/레벨/달성 일시/연결 보상</t>
+          <t xml:space="preserve">그룹/시즌/레벨/레벨업 일시/연결 보상</t>
         </is>
       </c>
     </row>
@@ -30965,7 +30965,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달성 일시 내림차순(최신순)</t>
+          <t xml:space="preserve">레벨업 일시 내림차순(최신순)</t>
         </is>
       </c>
     </row>
@@ -31648,7 +31648,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -31770,12 +31770,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">탭 메뉴 3종</t>
+          <t xml:space="preserve">탭 메뉴 4종</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랭킹 시즌 설정 / 덕력 랭킹 / 덕력 내역, 첫 진입 시 '랭킹 시즌 설정' 활성</t>
+          <t xml:space="preserve">랭킹 시즌 설정 / 덕력 랭킹 / 덕력 내역 / 덕력 지급 정책, 첫 진입 시 '랭킹 시즌 설정' 활성</t>
         </is>
       </c>
     </row>
@@ -31813,7 +31813,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">?tab=season/ranking/history 반영, 새로고침 시 동일 탭 복원, 잘못된 쿼리는 기본 탭 복귀</t>
+          <t xml:space="preserve">?tab=season/ranking/history/policy 반영, 새로고침 시 동일 탭 복원, 잘못된 쿼리는 기본 탭 복귀</t>
         </is>
       </c>
     </row>
@@ -34780,28 +34780,28 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">권한</t>
+          <t xml:space="preserve">지급 정책</t>
         </is>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">덕력관리</t>
+          <t xml:space="preserve">덕력 지급 정책</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">모달확인</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">쓰기 권한 없음</t>
+          <t xml:space="preserve">상세에서 [덕력 지급 정책] 탭 클릭(?tab=policy)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[신규 시즌]·[수정]·[강제 종료]·[상태 변경]·보상 편집 버튼 미노출</t>
+          <t xml:space="preserve">지급 정책 탭 전환, 그룹 선택 + 자동 적립 활동 매트릭스</t>
         </is>
       </c>
     </row>
@@ -34818,28 +34818,28 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">권한</t>
+          <t xml:space="preserve">지급 정책</t>
         </is>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">덕력관리</t>
+          <t xml:space="preserve">덕력 지급 정책</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">외부 협력사 권한</t>
+          <t xml:space="preserve">안내·그룹 선택·액션</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">본인 매핑 소속사 산하 그룹 시즌·랭킹·내역만 조회</t>
+          <t xml:space="preserve">'아티스트 그룹별 자동 적립 활동 덕력 지급량 설정, Quest·게임은 콘텐츠 직접 입력' 안내 + 그룹 드롭다운 + [권장값 적용]·[저장]</t>
         </is>
       </c>
     </row>
@@ -34856,32 +34856,32 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동</t>
+          <t xml:space="preserve">지급 정책</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랭킹</t>
+          <t xml:space="preserve">매트릭스</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+          <t xml:space="preserve">덕력 지급 정책</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동 확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시즌 등록 → 앱</t>
+          <t xml:space="preserve">매트릭스 컬럼</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 덕력 랭킹에 시즌 노출, 다국어 시즌명 로케일별 표시</t>
+          <t xml:space="preserve">활동·티어 배지·권장값(읽기 전용)·지급 덕력(입력)·사용 여부 토글</t>
         </is>
       </c>
     </row>
@@ -34898,32 +34898,32 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동</t>
+          <t xml:space="preserve">지급 정책</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랭킹</t>
+          <t xml:space="preserve">매트릭스</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+          <t xml:space="preserve">덕력 지급 정책</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동 확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랭킹 산정 → 앱</t>
+          <t xml:space="preserve">대상 활동 9종</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시즌별 획득 덕력 누적 기준 순위, BO 랭킹과 일치</t>
+          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유·기억저장소 업로드·디지털 굿즈 획득·스트릭 7/14/30(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
         </is>
       </c>
     </row>
@@ -34940,32 +34940,32 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동</t>
+          <t xml:space="preserve">지급 정책</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보상</t>
+          <t xml:space="preserve">매트릭스</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+          <t xml:space="preserve">덕력 지급 정책</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동 확인</t>
+          <t xml:space="preserve">데이터입력</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상명·아이콘 → 앱</t>
+          <t xml:space="preserve">그룹 선택 전환</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BO 설정 다국어 대상명·아이콘이 앱 보상 안내에 로케일별 노출</t>
+          <t xml:space="preserve">선택 그룹 정책으로 매트릭스 교체, 미저장 변경 시 이동 확인</t>
         </is>
       </c>
     </row>
@@ -34982,32 +34982,32 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동</t>
+          <t xml:space="preserve">지급 정책</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정산</t>
+          <t xml:space="preserve">매트릭스</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+          <t xml:space="preserve">덕력 지급 정책</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">앱 연동 확인</t>
+          <t xml:space="preserve">데이터입력</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시즌 말일 자동 정산 → 앱</t>
+          <t xml:space="preserve">지급 덕력 입력</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">말일 23:59 서버 자동 정산, 보상 지급</t>
+          <t xml:space="preserve">0 이상 정수, 권장값과 다르면 강조 표시</t>
         </is>
       </c>
     </row>
@@ -35024,32 +35024,612 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매트릭스</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에러 메시지 확인</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음수·소수·문자 입력</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'지급 덕력은 0 이상 정수여야 합니다.' 인라인 + [저장] 차단</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0082</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매트릭스</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용 여부 토글</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사용↔미사용 전환, 미사용 시 해당 활동 미지급(미사용 시 입력 비활성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0083</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매트릭스</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[권장값 적용]</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전 활동 권장값(T1 5/T2 25/T3 75·스트릭 200/500/1,000)·사용 ON 일괄 채움</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0084</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변경 감지</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 덕력·사용 여부 변경 시 [저장] 활성, 변경 없으면 비활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0085</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">저장</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[저장] → 확인</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">'지급 정책을 저장할까요?' 모달 → 저장(이후 적립부터 반영) + 토스트 + 마지막 수정 정보·활동 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0086</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자동 생성</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규 아티스트 기본 정책</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">신규 아티스트 생성 시 권장값 기본 정책 자동 생성·사용 ON → '미설정' 상태 부재(항상 9개 활동 행 노출)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0087</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loading / 오류 / 권한 없음</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skeleton / '지급 정책을 불러오지 못했습니다.'+[다시 시도] / 쓰기 권한 없으면 입력·토글·버튼 비활성</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0088</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">권한</t>
+        </is>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쓰기 권한 없음</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[신규 시즌]·[수정]·[강제 종료]·[상태 변경]·보상 편집 버튼 미노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0089</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">권한</t>
+        </is>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">외부 협력사 권한</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">본인 매핑 소속사 산하 그룹 시즌·랭킹·내역만 조회</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0090</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">앱 연동</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랭킹</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시즌 등록 → 앱</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 랭킹에 시즌 노출, 다국어 시즌명 로케일별 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랭킹</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랭킹 산정 → 앱</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시즌별 획득 덕력 누적 기준 순위, BO 랭킹과 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">보상</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상명·아이콘 → 앱</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BO 설정 다국어 대상명·아이콘이 앱 보상 안내에 로케일별 노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정산</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시즌 말일 자동 정산 → 앱</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">말일 23:59 서버 자동 정산, 보상 지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">강제 종료</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">앱 덕력 랭킹(DUK)</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">강제 종료 → 앱</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">보상 미지급, 강제 종료 시즌 랭킹은 앱에서 아카이브 조회 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 적립</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책 저장 → 앱</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아티스트별 활동 덕력 지급량·사용 여부가 회원 활동 적립에 반영(이후 적립부터, 소급 없음). 미사용 활동은 미지급</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -13598,7 +13598,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석·일일미션·스트릭 보상과 미션 풀 운영 설명 노출</t>
+          <t xml:space="preserve">미션 풀·하루 제시 미션 수 운영 설명 노출(덕력 지급량은 지급 정책 참조)</t>
         </is>
       </c>
     </row>
@@ -13989,17 +13989,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석 체크 보상 필드 노출</t>
+          <t xml:space="preserve">하루 제시 미션 수에 0 입력</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">숫자 입력 필드(단위: 덕력) 노출</t>
+          <t xml:space="preserve">정수 유효성 안내 + [변경사항 저장] 비활성</t>
         </is>
       </c>
     </row>
@@ -14031,17 +14031,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 전체 완료 보상 필드 노출</t>
+          <t xml:space="preserve">하루 제시 미션 수에 음수 입력</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">숫자 입력 필드(단위: 덕력) 노출</t>
+          <t xml:space="preserve">유효성 안내 + [변경사항 저장] 비활성</t>
         </is>
       </c>
     </row>
@@ -14078,12 +14078,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하루 제시 미션 수에 0 입력</t>
+          <t xml:space="preserve">하루 제시 미션 수에 텍스트·소수 입력</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정수 유효성 안내 + [변경사항 저장] 비활성</t>
+          <t xml:space="preserve">유효성 안내 + [변경사항 저장] 비활성</t>
         </is>
       </c>
     </row>
@@ -14120,12 +14120,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하루 제시 미션 수에 음수 입력</t>
+          <t xml:space="preserve">하루 제시 수 &gt; 사용 중인 미션 수로 설정</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효성 안내 + [변경사항 저장] 비활성</t>
+          <t xml:space="preserve">(사전조건) 사용 중 미션 N건. '사용 중인 미션이 N건이라 매일 최대 N건만 제시됩니다' 경고(저장 가능)</t>
         </is>
       </c>
     </row>
@@ -14147,7 +14147,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 설정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하루 제시 미션 수에 텍스트·소수 입력</t>
+          <t xml:space="preserve">미션 풀 섹션 헤더 확인</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효성 안내 + [변경사항 저장] 비활성</t>
+          <t xml:space="preserve">'미션 풀 (사용 N종 / 전체 M종)' + [미션 추가] 버튼 노출</t>
         </is>
       </c>
     </row>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 설정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -14199,17 +14199,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석 체크 보상에 음수 입력</t>
+          <t xml:space="preserve">시스템 자동 선택 안내 박스 확인</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효성 안내 + 저장 비활성(0은 허용)</t>
+          <t xml:space="preserve">전일 중복 회피·당일 상이·부족 시 미노출 안내 노출</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14231,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 설정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -14241,17 +14241,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 완료 보상에 음수 입력</t>
+          <t xml:space="preserve">미션 풀 테이블 컬럼 헤더 확인</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효성 안내 + 저장 비활성(0은 허용)</t>
+          <t xml:space="preserve">미션명 / 이동 대상 / 사용여부 / 관리 컬럼 노출</t>
         </is>
       </c>
     </row>
@@ -14273,7 +14273,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 설정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -14283,17 +14283,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하루 제시 수 &gt; 사용 중인 미션 수로 설정</t>
+          <t xml:space="preserve">미션 행 - 미션명 셀</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 사용 중 미션 N건. '사용 중인 미션이 N건이라 매일 최대 N건만 제시됩니다' 경고(저장 가능)</t>
+          <t xml:space="preserve">미션명 + (있으면) 설명 보조텍스트 표시</t>
         </is>
       </c>
     </row>
@@ -14330,12 +14330,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀 섹션 헤더 확인</t>
+          <t xml:space="preserve">미션 행 - 이동 대상 셀</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'미션 풀 (사용 N종 / 전체 M종)' + [미션 추가] 버튼 노출</t>
+          <t xml:space="preserve">이동 대상 화면명 표시</t>
         </is>
       </c>
     </row>
@@ -14372,12 +14372,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시스템 자동 선택 안내 박스 확인</t>
+          <t xml:space="preserve">미션 행 - 준비 중 대상 표시</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전일 중복 회피·당일 상이·부족 시 미노출 안내 노출</t>
+          <t xml:space="preserve">이동 대상이 준비 중(Coming Soon)이면 '준비 중' 표시</t>
         </is>
       </c>
     </row>
@@ -14414,12 +14414,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀 테이블 컬럼 헤더 확인</t>
+          <t xml:space="preserve">미션 행 - 사용여부 토글</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 / 이동 대상 / 사용여부 / 관리 컬럼 노출</t>
+          <t xml:space="preserve">사용/미사용 토글 스위치 표시</t>
         </is>
       </c>
     </row>
@@ -14456,12 +14456,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 행 - 미션명 셀</t>
+          <t xml:space="preserve">미션 행 - 관리 버튼</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 + (있으면) 설명 보조텍스트 표시</t>
+          <t xml:space="preserve">행별 [수정][삭제] 버튼 표시</t>
         </is>
       </c>
     </row>
@@ -14483,27 +14483,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">모달확인</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 행 - 이동 대상 셀</t>
+          <t xml:space="preserve">[미션 추가] 버튼 클릭</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이동 대상 화면명 표시</t>
+          <t xml:space="preserve">추가 모달 진입, 타이틀 '일일미션 추가'</t>
         </is>
       </c>
     </row>
@@ -14525,12 +14525,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -14540,12 +14540,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 행 - 준비 중 대상 표시</t>
+          <t xml:space="preserve">미션명 다국어 입력 영역 확인</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이동 대상이 준비 중(Coming Soon)이면 '준비 중' 표시</t>
+          <t xml:space="preserve">한국어/영어/일본어 탭 + 입력 필드 노출</t>
         </is>
       </c>
     </row>
@@ -14567,12 +14567,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 행 - 사용여부 토글</t>
+          <t xml:space="preserve">미션명 다국어 탭 입력 상태 표시</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용/미사용 토글 스위치 표시</t>
+          <t xml:space="preserve">입력 완료 언어 탭에 ✓ 표시</t>
         </is>
       </c>
     </row>
@@ -14609,12 +14609,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">미션 추가·수정</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -14624,12 +14624,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 행 - 관리 버튼</t>
+          <t xml:space="preserve">설명 다국어 입력 영역(선택) 확인</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">행별 [수정][삭제] 버튼 표시</t>
+          <t xml:space="preserve">한국어/영어/일본어 설명 필드 노출(선택 입력)</t>
         </is>
       </c>
     </row>
@@ -14661,17 +14661,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모달확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[미션 추가] 버튼 클릭</t>
+          <t xml:space="preserve">이동 대상 드롭다운 옵션 확인</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추가 모달 진입, 타이틀 '일일미션 추가'</t>
+          <t xml:space="preserve">8종(아티스트 메인·게임존·기억저장소·덕력 랭킹·래플·컬렉션·서포트·정보 피드) 노출</t>
         </is>
       </c>
     </row>
@@ -14708,12 +14708,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 다국어 입력 영역 확인</t>
+          <t xml:space="preserve">드롭다운 준비 중 대상 표시</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국어/영어/일본어 탭 + 입력 필드 노출</t>
+          <t xml:space="preserve">준비 중 대상은 '(준비 중)' 표시</t>
         </is>
       </c>
     </row>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 다국어 탭 입력 상태 표시</t>
+          <t xml:space="preserve">사용여부 라디오 기본값 확인</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">입력 완료 언어 탭에 ✓ 표시</t>
+          <t xml:space="preserve">기본 '사용' 선택</t>
         </is>
       </c>
     </row>
@@ -14792,12 +14792,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">설명 다국어 입력 영역(선택) 확인</t>
+          <t xml:space="preserve">모달 버튼 노출 확인</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">한국어/영어/일본어 설명 필드 노출(선택 입력)</t>
+          <t xml:space="preserve">[추가하기]/[취소하기]/[X] 노출</t>
         </is>
       </c>
     </row>
@@ -14829,17 +14829,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이동 대상 드롭다운 옵션 확인</t>
+          <t xml:space="preserve">미션명 한국어만 입력(영·일 미입력)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8종(아티스트 메인·게임존·기억저장소·덕력 랭킹·래플·컬렉션·서포트·정보 피드) 노출</t>
+          <t xml:space="preserve">[추가하기] 비활성</t>
         </is>
       </c>
     </row>
@@ -14871,17 +14871,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">드롭다운 준비 중 대상 표시</t>
+          <t xml:space="preserve">미션명 영어 미입력</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">준비 중 대상은 '(준비 중)' 표시</t>
+          <t xml:space="preserve">[추가하기] 비활성</t>
         </is>
       </c>
     </row>
@@ -14913,17 +14913,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용여부 라디오 기본값 확인</t>
+          <t xml:space="preserve">미션명 일본어 미입력</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기본 '사용' 선택</t>
+          <t xml:space="preserve">[추가하기] 비활성</t>
         </is>
       </c>
     </row>
@@ -14955,17 +14955,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">데이터입력</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모달 버튼 노출 확인</t>
+          <t xml:space="preserve">미션명 50자 초과 입력 시도</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[추가하기]/[취소하기]/[X] 노출</t>
+          <t xml:space="preserve">언어별 50자 제한(초과 입력 차단)</t>
         </is>
       </c>
     </row>
@@ -14997,17 +14997,17 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">데이터입력</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 한국어만 입력(영·일 미입력)</t>
+          <t xml:space="preserve">설명 60자 초과 입력 시도</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[추가하기] 비활성</t>
+          <t xml:space="preserve">언어별 60자 제한(초과 입력 차단)</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 영어 미입력</t>
+          <t xml:space="preserve">이동 대상 미선택</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -15086,12 +15086,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 일본어 미입력</t>
+          <t xml:space="preserve">추가 시 다른 미션과 동일한 이동 대상 선택</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[추가하기] 비활성</t>
+          <t xml:space="preserve">'이미 같은 이동 대상을 사용하는 미션이 있습니다' 경고 + 버튼 비활성</t>
         </is>
       </c>
     </row>
@@ -15123,17 +15123,17 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션명 50자 초과 입력 시도</t>
+          <t xml:space="preserve">준비 중(Coming Soon) 대상 선택</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">언어별 50자 제한(초과 입력 차단)</t>
+          <t xml:space="preserve">'앱 노출 전까지 미션 선택에서 제외' 회색 안내 + 저장 허용</t>
         </is>
       </c>
     </row>
@@ -15170,12 +15170,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">설명 60자 초과 입력 시도</t>
+          <t xml:space="preserve">필수 입력(미션명 3언어+이동 대상) 후 [추가하기]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">언어별 60자 제한(초과 입력 차단)</t>
+          <t xml:space="preserve">미션 풀에 추가 + '일일미션이 추가되었습니다' 토스트 + 모달 닫힘</t>
         </is>
       </c>
     </row>
@@ -15207,17 +15207,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">백오피스 액션</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이동 대상 미선택</t>
+          <t xml:space="preserve">미션 추가 후 활동 로그 확인</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[추가하기] 비활성</t>
+          <t xml:space="preserve">'일일미션 {미션명}을(를) 추가했습니다 (이동 대상: {대상})' 로그</t>
         </is>
       </c>
     </row>
@@ -15249,17 +15249,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">모달확인</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추가 시 다른 미션과 동일한 이동 대상 선택</t>
+          <t xml:space="preserve">미션 행 [수정] 버튼 클릭</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'이미 같은 이동 대상을 사용하는 미션이 있습니다' 경고 + 버튼 비활성</t>
+          <t xml:space="preserve">수정 모달 진입, 타이틀 '일일미션 수정', 기존값 채워짐</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">준비 중(Coming Soon) 대상 선택</t>
+          <t xml:space="preserve">수정 시 자기 자신의 기존 이동 대상 유지</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'앱 노출 전까지 미션 선택에서 제외' 회색 안내 + 저장 허용</t>
+          <t xml:space="preserve">중복 경고 없음(자기 제외), [저장하기] 활성</t>
         </is>
       </c>
     </row>
@@ -15333,17 +15333,17 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수 입력(미션명 3언어+이동 대상) 후 [추가하기]</t>
+          <t xml:space="preserve">수정 시 다른 미션의 대상으로 변경(중복)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀에 추가 + '일일미션이 추가되었습니다' 토스트 + 모달 닫힘</t>
+          <t xml:space="preserve">중복 경고 + 버튼 비활성</t>
         </is>
       </c>
     </row>
@@ -15375,17 +15375,17 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">백오피스 액션</t>
+          <t xml:space="preserve">데이터입력</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가 후 활동 로그 확인</t>
+          <t xml:space="preserve">미션 수정 후 [저장하기]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'일일미션 {미션명}을(를) 추가했습니다 (이동 대상: {대상})' 로그</t>
+          <t xml:space="preserve">행 갱신 + '일일미션이 수정되었습니다' 토스트</t>
         </is>
       </c>
     </row>
@@ -15417,17 +15417,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모달확인</t>
+          <t xml:space="preserve">상태확인</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 행 [수정] 버튼 클릭</t>
+          <t xml:space="preserve">이동 대상 수정 정책(당일 배정) 확인</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 모달 진입, 타이틀 '일일미션 수정', 기존값 채워짐</t>
+          <t xml:space="preserve">당일 배정 회원 미션 유지, 변경은 다음날 자정 재선택부터 반영(소급 없음)</t>
         </is>
       </c>
     </row>
@@ -15449,27 +15449,27 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">버튼클릭</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 시 자기 자신의 기존 이동 대상 유지</t>
+          <t xml:space="preserve">사용여부 토글(사용→미사용)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중복 경고 없음(자기 제외), [저장하기] 활성</t>
+          <t xml:space="preserve">즉시 전환 + '{미션명}을(를) 미사용으로 전환했습니다' 토스트</t>
         </is>
       </c>
     </row>
@@ -15491,27 +15491,27 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">버튼클릭</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 시 다른 미션의 대상으로 변경(중복)</t>
+          <t xml:space="preserve">사용여부 토글(미사용→사용)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">중복 경고 + 버튼 비활성</t>
+          <t xml:space="preserve">즉시 전환 + 완료 토스트</t>
         </is>
       </c>
     </row>
@@ -15533,27 +15533,27 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">모달확인</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 수정 후 [저장하기]</t>
+          <t xml:space="preserve">(사전조건) 사용 미션 1건만 남긴 상태에서 그 미션 미사용 전환 시도</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">행 갱신 + '일일미션이 수정되었습니다' 토스트</t>
+          <t xml:space="preserve">0건화 확인 모달 '사용 미션 0건 → 앱 미표시. 계속할까요?' 노출</t>
         </is>
       </c>
     </row>
@@ -15575,27 +15575,27 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가·수정</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">버튼클릭</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이동 대상 수정 정책(당일 배정) 확인</t>
+          <t xml:space="preserve">0건화 확인 모달 [확인]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">당일 배정 회원 미션 유지, 변경은 다음날 자정 재선택부터 반영(소급 없음)</t>
+          <t xml:space="preserve">미사용 전환 진행 + 토스트</t>
         </is>
       </c>
     </row>
@@ -15632,12 +15632,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용여부 토글(사용→미사용)</t>
+          <t xml:space="preserve">0건화 확인 모달 [취소]</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">즉시 전환 + '{미션명}을(를) 미사용으로 전환했습니다' 토스트</t>
+          <t xml:space="preserve">전환 취소, 사용 상태 유지</t>
         </is>
       </c>
     </row>
@@ -15659,27 +15659,27 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼클릭</t>
+          <t xml:space="preserve">모달확인</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사용여부 토글(미사용→사용)</t>
+          <t xml:space="preserve">미션 행 [삭제] 버튼 클릭</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">즉시 전환 + 완료 토스트</t>
+          <t xml:space="preserve">삭제 모달 진입, '미션을 삭제하시겠어요?' + 본문(다음날 제외·당일 배정 유지)</t>
         </is>
       </c>
     </row>
@@ -15701,27 +15701,27 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모달확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 사용 미션 1건만 남긴 상태에서 그 미션 미사용 전환 시도</t>
+          <t xml:space="preserve">(사전조건) 사용 미션 1건만 남긴 상태에서 그 미션 삭제 모달 진입</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0건화 확인 모달 '사용 미션 0건 → 앱 미표시. 계속할까요?' 노출</t>
+          <t xml:space="preserve">기본 본문 + '삭제 후 사용 미션 0건 → 앱 미표시' 경고 추가</t>
         </is>
       </c>
     </row>
@@ -15743,27 +15743,27 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼클릭</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0건화 확인 모달 [확인]</t>
+          <t xml:space="preserve">삭제 모달 버튼 노출 확인</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미사용 전환 진행 + 토스트</t>
+          <t xml:space="preserve">[삭제하기]/[취소하기]/[X] 노출</t>
         </is>
       </c>
     </row>
@@ -15785,12 +15785,12 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 풀</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">삭제 확인</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -15800,12 +15800,12 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0건화 확인 모달 [취소]</t>
+          <t xml:space="preserve">삭제 모달 [삭제하기]</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전환 취소, 사용 상태 유지</t>
+          <t xml:space="preserve">미션 제거 + '일일미션이 삭제되었습니다' 토스트</t>
         </is>
       </c>
     </row>
@@ -15837,17 +15837,17 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모달확인</t>
+          <t xml:space="preserve">버튼클릭</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 행 [삭제] 버튼 클릭</t>
+          <t xml:space="preserve">삭제 모달 [취소하기]/[X]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 모달 진입, '미션을 삭제하시겠어요?' + 본문(다음날 제외·당일 배정 유지)</t>
+          <t xml:space="preserve">삭제 취소, 미션 유지</t>
         </is>
       </c>
     </row>
@@ -15879,17 +15879,17 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">상태확인</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 사용 미션 1건만 남긴 상태에서 그 미션 삭제 모달 진입</t>
+          <t xml:space="preserve">삭제 정책(당일 배정) 확인</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기본 본문 + '삭제 후 사용 미션 0건 → 앱 미표시' 경고 추가</t>
+          <t xml:space="preserve">당일 배정 회원 미션 유지·완료 인정, 다음날 자정부터 제외</t>
         </is>
       </c>
     </row>
@@ -15911,27 +15911,27 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 확인</t>
+          <t xml:space="preserve">미션 풀</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 확인</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">상태확인</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 모달 버튼 노출 확인</t>
+          <t xml:space="preserve">(사전조건) 미션 풀 전체 삭제 후 목록 확인</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[삭제하기]/[취소하기]/[X] 노출</t>
+          <t xml:space="preserve">'등록된 미션이 없습니다. [미션 추가]로 미션 풀을 구성하세요.' Empty 메시지</t>
         </is>
       </c>
     </row>
@@ -15953,27 +15953,27 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 확인</t>
+          <t xml:space="preserve">스트릭</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 확인</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼클릭</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 모달 [삭제하기]</t>
+          <t xml:space="preserve">스트릭 안내 문구 확인</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 제거 + '일일미션이 삭제되었습니다' 토스트</t>
+          <t xml:space="preserve">28일 주기(4주) 순환·마일스톤 고정(7/14/21/28일)·덕력 지급량은 지급 정책 소관·28일 도달 후 다음날 1일차 초기화 안내(읽기 전용)</t>
         </is>
       </c>
     </row>
@@ -15995,27 +15995,27 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 확인</t>
+          <t xml:space="preserve">스트릭</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 확인</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼클릭</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 모달 [취소하기]/[X]</t>
+          <t xml:space="preserve">스트릭 마일스톤 노출 확인</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 취소, 미션 유지</t>
+          <t xml:space="preserve">스트릭 마일스톤은 7/14/21/28일 4종만 안내(읽기 전용), 100일 없음</t>
         </is>
       </c>
     </row>
@@ -16035,14 +16035,10 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삭제 확인</t>
-        </is>
-      </c>
+      <c r="D59" s="2"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 확인</t>
+          <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -16052,12 +16048,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 정책(당일 배정) 확인</t>
+          <t xml:space="preserve">변경 없는 초기 상태의 [변경사항 저장]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">당일 배정 회원 미션 유지·완료 인정, 다음날 자정부터 제외</t>
+          <t xml:space="preserve">비활성</t>
         </is>
       </c>
     </row>
@@ -16077,11 +16073,7 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미션 풀</t>
-        </is>
-      </c>
+      <c r="D60" s="2"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일일미션 관리</t>
@@ -16094,12 +16086,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 미션 풀 전체 삭제 후 목록 확인</t>
+          <t xml:space="preserve">하루 제시 미션 수 변경 시 [변경사항 저장]</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'등록된 미션이 없습니다. [미션 추가]로 미션 풀을 구성하세요.' Empty 메시지</t>
+          <t xml:space="preserve">활성</t>
         </is>
       </c>
     </row>
@@ -16119,11 +16111,7 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
+      <c r="D61" s="2"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일일미션 관리</t>
@@ -16131,17 +16119,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">상태확인</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스트릭 보너스 안내 문구 확인</t>
+          <t xml:space="preserve">변경 후 원래 값으로 복원 시 [변경사항 저장]</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30일 주기 순환·마일스톤 고정·보상값만 조정·30일 도달 후 다음날 1일차 초기화 안내</t>
+          <t xml:space="preserve">다시 비활성</t>
         </is>
       </c>
     </row>
@@ -16161,11 +16149,7 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
+      <c r="D62" s="2"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일일미션 관리</t>
@@ -16173,17 +16157,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">상태확인</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">연속 7일 보상 필드 노출</t>
+          <t xml:space="preserve">입력 오류가 존재할 때 [변경사항 저장]</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보상값 입력 필드(기본 200) 노출</t>
+          <t xml:space="preserve">비활성</t>
         </is>
       </c>
     </row>
@@ -16203,11 +16187,7 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
+      <c r="D63" s="2"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일일미션 관리</t>
@@ -16215,17 +16195,17 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">모달확인</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">연속 14일 보상 필드 노출</t>
+          <t xml:space="preserve">변경 후 [변경사항 저장] 클릭</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보상값 입력 필드(기본 500) 노출</t>
+          <t xml:space="preserve">변경 요약 확인 모달 노출(변경 항목 목록 표시)</t>
         </is>
       </c>
     </row>
@@ -16245,11 +16225,7 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
+      <c r="D64" s="2"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일일미션 관리</t>
@@ -16257,17 +16233,17 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">데이터입력</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">연속 30일 보상 필드 노출</t>
+          <t xml:space="preserve">변경 요약 모달 [확인]</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보상값 입력 필드(기본 1,000) 노출</t>
+          <t xml:space="preserve">일괄 저장 + '일일미션 설정을 변경했습니다 (변경 항목: …)' 토스트</t>
         </is>
       </c>
     </row>
@@ -16287,11 +16263,7 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
+      <c r="D65" s="2"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일일미션 관리</t>
@@ -16299,17 +16271,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">버튼클릭</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100일 마일스톤 필드 미노출 확인</t>
+          <t xml:space="preserve">변경 요약 모달 [취소]</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스트릭 입력 필드는 7/14/30일 3종만, 100일 필드 없음</t>
+          <t xml:space="preserve">저장 취소, 미저장 상태 유지</t>
         </is>
       </c>
     </row>
@@ -16329,11 +16301,7 @@
           <t xml:space="preserve">일일미션 관리</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
+      <c r="D66" s="2"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">일일미션 관리</t>
@@ -16341,17 +16309,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">백오피스 액션</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">스트릭 보상값에 음수 입력</t>
+          <t xml:space="preserve">설정 저장 후 활동 로그</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효성 안내 + 저장 비활성(0은 허용)</t>
+          <t xml:space="preserve">'일일미션 설정을 변경했습니다 (변경 항목: …)' 로그</t>
         </is>
       </c>
     </row>
@@ -16379,17 +16347,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 없는 초기 상태의 [변경사항 저장]</t>
+          <t xml:space="preserve">설정 저장 실패 시</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비활성</t>
+          <t xml:space="preserve">'저장에 실패했습니다' 토스트(입력값 유지) (실패 유발: 저장 직전 네트워크 오프라인)</t>
         </is>
       </c>
     </row>
@@ -16422,12 +16390,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">설정·스트릭 값 변경 시 [변경사항 저장]</t>
+          <t xml:space="preserve">미저장 변경 후 페이지 이탈·새로고침 시도</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성</t>
+          <t xml:space="preserve">'저장하지 않은 변경사항이 있습니다' 이탈 가드 노출</t>
         </is>
       </c>
     </row>
@@ -16444,28 +16412,32 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D69" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미션 풀</t>
+        </is>
+      </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 후 원래 값으로 복원 시 [변경사항 저장]</t>
+          <t xml:space="preserve">BO에서 미션 추가 → 앱 미션 풀</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">다시 비활성</t>
+          <t xml:space="preserve">추가 미션이 앱 미션 풀 후보에 노출(당일 배정 유지, 변경은 다음날 자정 반영) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16482,28 +16454,32 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D70" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미션 풀</t>
+        </is>
+      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">입력 오류가 존재할 때 [변경사항 저장]</t>
+          <t xml:space="preserve">BO에서 미션 삭제 → 앱</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비활성</t>
+          <t xml:space="preserve">당일 배정분 유지·완료 인정, 다음날 자정부터 제외 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16520,28 +16496,32 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D71" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미션 풀</t>
+        </is>
+      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모달확인</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 후 [변경사항 저장] 클릭</t>
+          <t xml:space="preserve">BO에서 미션 미사용 전환 → 앱</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 요약 확인 모달 노출(변경 항목 목록 표시)</t>
+          <t xml:space="preserve">다음날 자정부터 미션 선택에서 제외 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16558,28 +16538,32 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D72" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일일미션 설정</t>
+        </is>
+      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보상값 0 포함 변경 후 [변경사항 저장]</t>
+          <t xml:space="preserve">하루 제시 미션 수 변경 → 앱</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 요약에 '보상이 0 덕력입니다(보상 없이 동작)' 안내 노출</t>
+          <t xml:space="preserve">다음날 자정부터 변경된 수만큼 제시 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16596,28 +16580,32 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D73" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미션 풀</t>
+        </is>
+      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 요약 모달 [확인]</t>
+          <t xml:space="preserve">사용 미션이 0건일 때 → 앱</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일괄 저장 + '일일미션 설정을 변경했습니다 (변경 항목: …)' 토스트</t>
+          <t xml:space="preserve">앱 일일미션 카드 숨김, 출석 체크만 노출 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16634,28 +16622,32 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D74" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미션 풀</t>
+        </is>
+      </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼클릭</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">변경 요약 모달 [취소]</t>
+          <t xml:space="preserve">Coming Soon 대상 미션 → 앱</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">저장 취소, 미저장 상태 유지</t>
+          <t xml:space="preserve">앱 미션 선택에서 자동 제외, 서비스 오픈 시 선택 가능 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16672,28 +16664,32 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D75" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스트릭</t>
+        </is>
+      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">백오피스 액션</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">설정 저장 후 활동 로그</t>
+          <t xml:space="preserve">스트릭 28일 주기 순환 → 앱</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'일일미션 설정을 변경했습니다 (변경 항목: …)' 로그</t>
+          <t xml:space="preserve">28일 도달 보너스 후 다음날 1일차 초기화, 7/14/21/28일 매 주기 반복 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16710,28 +16706,32 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D76" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스트릭</t>
+        </is>
+      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">설정 저장 실패 시</t>
+          <t xml:space="preserve">스트릭 출석 끊김 → 앱</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'저장에 실패했습니다' 토스트(입력값 유지) (실패 유발: 저장 직전 네트워크 오프라인)</t>
+          <t xml:space="preserve">연속 일수 0으로 초기화(주기 무관) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -16748,574 +16748,32 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
-        </is>
-      </c>
-      <c r="D77" s="2"/>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 귀속</t>
+        </is>
+      </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">일일미션 관리</t>
+          <t xml:space="preserve">앱 일일 미션</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미저장 변경 후 페이지 이탈·새로고침 시도</t>
+          <t xml:space="preserve">(사전조건) 선택 아티스트 그룹 덕력 지급 정책 설정, 데일리 루프(출석·일일미션·스트릭) 수행 → 앱</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'저장하지 않은 변경사항이 있습니다' 이탈 가드 노출</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0077</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미션 풀</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BO에서 미션 추가 → 앱 미션 풀</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">추가 미션이 앱 미션 풀 후보에 노출(당일 배정 유지, 변경은 다음날 자정 반영) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0078</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미션 풀</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BO에서 미션 삭제 → 앱</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">당일 배정분 유지·완료 인정, 다음날 자정부터 제외 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0079</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미션 풀</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BO에서 미션 미사용 전환 → 앱</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다음날 자정부터 미션 선택에서 제외 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0080</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션 설정</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하루 제시 미션 수 변경 → 앱</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다음날 자정부터 변경된 수만큼 제시 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0081</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션 설정</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">출석 체크 보상값 변경 → 앱</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">적용 이후 출석부터 새 값 지급(소급 없음) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0082</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션 설정</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션 완료 보상값 변경 → 앱</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">적용 이후 완료부터 새 값 일괄 지급(소급 없음) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0083</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭 7일 보상값 변경 → 앱</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다음 도달부터 새 값 지급(소급 없음) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0084</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭 14일 보상값 변경 → 앱</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다음 도달부터 새 값 지급(소급 없음) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0085</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭 30일 보상값 변경 → 앱</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다음 도달부터 새 값 지급(소급 없음). 30일 후 다음날 1일차 초기화 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0086</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미션 풀</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사용 미션이 0건일 때 → 앱</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일미션 카드 숨김, 출석 체크만 노출 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0087</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">미션 풀</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Coming Soon 대상 미션 → 앱</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 미션 선택에서 자동 제외, 서비스 오픈 시 선택 가능 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0088</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭 30일 주기 순환 → 앱</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30일 도달 보너스 후 다음날 1일차 초기화, 7/14/30일 매 주기 반복 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_DLY_0089</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일일미션</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 일일 미션</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">스트릭 출석 끊김 → 앱</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">연속 일수 0으로 초기화(주기 무관) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
+          <t xml:space="preserve">출석·일일미션·스트릭 덕력은 선택(현재) 아티스트 그룹의 지급 정책([CEB-BO-ART-401-POLICY]) 기준으로 적립(일일미션 관리는 지급량 미설정). 미사용 활동은 미지급 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -35076,7 +34534,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -38346,12 +37804,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상 활동 9종</t>
+          <t xml:space="preserve">대상 활동 10종</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유·기억저장소 업로드·디지털 굿즈 획득·스트릭 7/14/30(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
+          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유·기억저장소 업로드·디지털 굿즈 획득·스트릭 7/14/21/28(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
         </is>
       </c>
     </row>
@@ -38561,7 +38019,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전 활동 권장값(T1 5/T2 25/T3 75·스트릭 200/500/1,000)·사용 ON 일괄 채움</t>
+          <t xml:space="preserve">전 활동 권장값(T1 5/T2 25/T3 75·스트릭 200/500/750/1,000)·사용 ON 일괄 채움</t>
         </is>
       </c>
     </row>
@@ -39310,6 +38768,48 @@
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">지급 정책 저장 시점 이후 적립부터 반영, 저장 전 활동은 소급 미적용(이전 적립값 유지) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데일리 루프 귀속</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 적립</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(사전조건) 그룹 지급 정책 설정, 회원이 선택 아티스트에서 출석·일일미션·스트릭 수행 → 앱</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데일리 루프 덕력이 선택(현재) 아티스트 그룹 정책에 따라 적립(미션은 계정 단위 1회 수행, 덕력은 활동 시점 선택 아티스트 귀속·[CEB-000] §5.2.2) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -108,7 +108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상↔정지 전환(쓰기 권한 시). 현 단계: 토글 동작·계정상태 전환만 검증 (권한 단계별 제재(경고~영구)는 제재 모달 구현 후)</t>
+          <t xml:space="preserve">정상↔정지 전환(쓰기 권한 시). 토글 동작·계정상태 전환만 검증</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검토 필요 배지·자산 회수 배너</t>
+          <t xml:space="preserve">검토 필요 배지</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 신고 누적·반복 반려·다중계정·비정상 응모 등 트리거 데이터 주입 / 자산 회수 이력 보유 회원. 트리거 충족 시 검토 필요 배지, 자산 회수 후 30일 배너 노출 (트리거 데이터 주입 불가 시 — 현 단계: 배지·배너 노출 영역 존재 여부만 검증)</t>
+          <t xml:space="preserve">(사전조건) 신고 누적·반복 반려·다중계정·비정상 응모 등 트리거 데이터 주입. 트리거 충족 시 기본정보 탭에 '검토 필요' 배지 노출 (트리거 데이터 주입 불가 시 — 현 단계: 배지 노출 영역 존재 여부만 검증)</t>
         </is>
       </c>
     </row>
@@ -2126,762 +2126,6 @@
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">배지 회색 전환, 이후 제재 시 미노출(이력 보존, 삭제 없음)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0048</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원 제재·자산(정책)</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원 상세(기본정보)</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI확인</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계·권한</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경고/부분/1·7일=운영자 / 30·90·영구·당첨취소·삭제=SUPER 전용. 정지사유 연동·다국어 알림. 현 단계: 화면 노출 여부만 검증 (동작은 제재 모달 구현 후)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0049</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원 제재·자산(정책)</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산 회수</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원 상세(기본정보)</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UI확인</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산 회수</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">덕력·응모권·BIVE·GP 회수, SUPER 전용·2FA, 회수 후 30일 배너·활동 로그. 현 단계: 화면 노출 여부만 검증 (동작은 자산 회수 모달 구현 후)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0050</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원 제재·자산(정책)</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">활동 로그</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원 상세(활동내역)</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">백오피스 액션</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재·자산 회수·메모·유저명 수정 로그</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">'{닉네임} {N}일 정지' / '덕력 {N}DUK 회수' / '메모 추가·수정' 등 활동 로그 기록. 현 단계: 활동내역 탭이 준비중이라 로그 화면 미노출(준비 중 안내) — 로그 적재·노출은 활동내역 탭·제재 모달 구현 후 검증</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0051</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 경고 제재 → 앱</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경고는 회원 알림만 발송, 앱 기능은 정상 유지(차단 없음) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0052</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 부분 정지(예 응모 차단) → 앱</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부분 정지 시 특정 기능만 비활성(예 래플 응모 차단), 그 외 앱 기능은 정상 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0053</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 임시 정지(1일) → 앱</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임시 정지(1일) 시 앱 전체 기능 차단, 1일 경과 시 자동 해제 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0054</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 임시 정지(7일) → 앱</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임시 정지(7일) 시 앱 전체 기능 차단, 7일 경과 시 자동 해제 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0055</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 임시 정지(30일) → 앱</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임시 정지(30일) 시 앱 전체 기능 차단, 30일 경과 시 자동 해제 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0056</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 임시 정지(90일) → 앱</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임시 정지(90일) 시 앱 전체 기능 차단, 90일 경과 시 자동 해제 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0057</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 영구 정지 → 앱</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">영구 정지 시 앱 전체 기능 영구 차단(자동 해제 없음) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0058</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재 단계</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 정상 회원 존재 — BO 계정 삭제 → 앱</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계정 삭제 시 앱 접근 불가, 개인정보보호 30일 유예 후 처리 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0059</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기한 만료</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 임시 정지 회원 존재 — 정지 기한 경과 → 앱</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">임시 정지 기한 경과 시 자동 해제, 앱 전체 기능 복구(실시간 동기화) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0060</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산 회수</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 덕력 보유 회원 존재 — BO 덕력 회수(SUPER) → 앱</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">덕력 잔액 즉시 차감(앱 반영), 회수 후 30일 배너 노출 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0061</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산 회수</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 응모권 보유 회원 존재 — BO 응모권 회수(SUPER) → 앱</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">응모권 잔액 즉시 차감(만료 오래된 것부터 차감, 앱 반영), 회수 후 30일 배너 노출 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0062</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산 회수</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) BIVE 보유 회원 존재 — BO BIVE 회수(SUPER) → 앱</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BIVE 보유 목록에서 제거(온체인 트랜잭션 처리, 앱 반영), 회수 후 30일 배너 노출 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0063</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산 회수</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) GP 보유 회원 존재 — BO GP 회수(SUPER) → 앱</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GP 잔액 즉시 차감(앱 반영), 회수 후 30일 배너 노출 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0064</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">알림</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 제재·자산 회수 처리 회원 존재 — BO 제재·자산 회수 → 회원 알림</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">제재·자산 회수 시 대상 회원에게 회원 언어(KO/EN/JA) 푸시+인앱 메시지 발송 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TC_USR_0065</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">회원</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">당첨 취소</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동(회원)</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">앱 연동 확인</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(사전조건) 당첨 이력 회원 존재 — BO 당첨 취소 → 앱</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해당 회원 래플 수령 비활성 유지(수령 불가) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -33778,7 +33778,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -37053,7 +37053,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유·기억저장소 업로드·디지털 굿즈 획득·스트릭 7/14/21/28(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
+          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유(기억 공유)·기억저장소 업로드·디지털 굿즈 획득·스트릭 7/14/21/28(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
         </is>
       </c>
     </row>
@@ -38054,6 +38054,48 @@
       <c r="H103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">데일리 루프 덕력이 선택(현재) 아티스트 그룹 정책에 따라 적립(미션은 계정 단위 1회 수행, 덕력은 활동 시점 선택 아티스트 귀속·[CEB-000] §5.2.2) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SNS 공유(기억 공유)</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 적립</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(사전조건) 그룹 지급 정책 SNS 공유 사용 ON, 본인 작성 기억 상세 우측 상단 공유 버튼 탭 → 앱</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SNS 공유 덕력 25 즉시 지급(외부 공유 완료 무관)·계정 1일 1회(00:00 KST 초기화)·당일 재공유 추가 없음(판단 기준=오늘 계정 지급 여부)·귀속=기억의 아티스트. 타인 기억 공유는 미지급 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -33778,7 +33778,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -37048,12 +37048,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상 활동 10종</t>
+          <t xml:space="preserve">대상 활동 15종</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유(기억 공유)·기억저장소 업로드·디지털 굿즈 획득·스트릭 7/14/21/28(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
+          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유(기억 공유)·기억저장소 업로드·디지털 굿즈 획득(등급별 Normal/Event/Special/Wicked/Next/Final 6)·스트릭 7/14/21/28(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
         </is>
       </c>
     </row>
@@ -37263,7 +37263,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전 활동 권장값(T1 5/T2 25/T3 75·스트릭 200/500/750/1,000)·사용 ON 일괄 채움</t>
+          <t xml:space="preserve">전 활동 권장값(T1 5/T2 25/T3 75·디지털 굿즈 획득 등급별 50/75/100/200/350/500·스트릭 200/500/750/1,000)·사용 ON 일괄 채움</t>
         </is>
       </c>
     </row>
@@ -38096,6 +38096,90 @@
       <c r="H104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SNS 공유 덕력 25 즉시 지급(외부 공유 완료 무관)·계정 1일 1회(00:00 KST 초기화)·당일 재공유 추가 없음(판단 기준=오늘 계정 지급 여부)·귀속=기억의 아티스트. 타인 기억 공유는 미지급 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지급 정책</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">매트릭스</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 지급 정책</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디지털 굿즈 획득 등급별 행 확인</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디지털 굿즈 획득이 BIVE 6등급 행(Normal/Event/Special/Wicked/Next/Final)으로 분리·각 권장값(50/75/100/200/350/500)·지급 덕력 입력·사용여부 토글</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_DUK_0105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력관리</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디지털 굿즈 획득</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 덕력 적립</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(사전조건) 그룹 정책 등급별 사용 ON — BIVE 민팅(획득) → 앱</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발행된 BIVE의 등급별 덕력 자동 적립(굿즈의 아티스트 귀속)·미사용 등급은 미적립. FIXED 동시 발행은 등급별 합산 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -52992,7 +53076,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -54384,6 +54468,48 @@
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">발행된 BIVE가 회원 보유 목록 추가·BSCScan에서 온체인 트랜잭션 조회 가능 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_BVM_0033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민팅 관리</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덕력 적립</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 BIVE 민팅</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(사전조건) 굿즈 아티스트 그룹 덕력 지급 정책 등급별 설정 — 자동 민팅 발행 → 덕력 적립</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">발행 BIVE의 등급별 덕력 자동 적립(사용 ON 등급만·굿즈의 아티스트 귀속, [CEB-BO-ART-401-POLICY]·[CEB-000] §5.2.4). FIXED 동시 발행은 등급별 합산 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -42088,7 +42088,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -44883,7 +44883,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">예측 마켓 선택 시 판정 유형 = 예측 참여 / 예측 정답</t>
+          <t xml:space="preserve">예측 마켓 선택 시 판정 유형 = 예측 참여 / 예측 정답. 두 유형 모두 기준 횟수 N 입력(참여형=N회 참여, 정답형=N번 예측 적중)</t>
         </is>
       </c>
     </row>
@@ -44925,7 +44925,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">서바이벌 트리비아 선택 시 판정 유형 = 트리비아 참여 / N회 정답(+기준 횟수 입력)</t>
+          <t xml:space="preserve">서바이벌 트리비아 선택 시 판정 유형 = 트리비아 참여 / 트리비아 승리. 두 유형 모두 기준 횟수 N 입력(참여형=N회 참여, 승리형=N번 승리). 트리비아 승리 = 게임 자체 생존(서바이벌 규칙) — 고정 임계치(7/10 등) 아님</t>
         </is>
       </c>
     </row>
@@ -46220,6 +46220,48 @@
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">설정한 반복 주기·기간 스케줄대로 앱 반영(주기마다 재참여) (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_EPI_0099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에피소드 그룹</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PM/ST 미션 완료</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 에피소드(SQ)</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">앱 연동 확인</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(사전조건) 진행중 에피소드의 예측 마켓·서바이벌 트리비아 미션 + 해당 아티스트 게임 진행, 회원이 그 아티스트 PM/ST 게임 참여(또는 정답) → 앱</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미션에 연결된 특정 게임 없이 판정 유형 × 기준 횟수 N에 따라 서버가 자동검증해 미션 자동 완료 — 참여형=N회 참여, 정답·승리형=N번 정답·승리(예측 정답=예측 적중, 트리비아 승리=게임 자체 생존(서바이벌 규칙), 고정 임계치 아님). 다른 아티스트 게임·해금 전 이력은 미인정 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -51800,7 +51800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -52603,7 +52603,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지(메인 필수+서브)/영상(MP4 50MB+썸네일 필수)/음성(MP3 10MB+썸네일 필수), 타입 변경 시 기존 파일 초기화</t>
+          <t xml:space="preserve">이미지(메인 이미지 필수+서브 이미지 선택+썸네일 필수)/영상(MP4 50MB+썸네일 필수)/음성(MP3 10MB+썸네일 필수), 타입 변경 시 기존 파일 초기화</t>
         </is>
       </c>
     </row>
@@ -52625,7 +52625,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기능설정 탭</t>
+          <t xml:space="preserve">기본정보 탭</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -52640,12 +52640,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">토글 3종</t>
+          <t xml:space="preserve">이미지 타입 썸네일 필드 노출</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">보내기(Send)·Mix·Pick(기본 ON)</t>
+          <t xml:space="preserve">이미지 타입 선택 시 메인 이미지·서브 이미지 grid 아래 '썸네일 ★' 박스 노출. 안내 'PNG/JPG/GIF/WebP · 최대 2MB · 권장 가로 640px · WebP 우선'</t>
         </is>
       </c>
     </row>
@@ -52667,7 +52667,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">검증</t>
+          <t xml:space="preserve">기본정보 탭</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -52677,17 +52677,17 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에러 메시지 확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수 누락 / 동일 조합 중복</t>
+          <t xml:space="preserve">썸네일 규격 통일</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'설정되지 않은 정보가 있습니다.' / 동일 (아티스트·등급·등급번호) 중복 에러</t>
+          <t xml:space="preserve">전 미디어 타입(이미지·영상·음성) 썸네일 동일 규격 — PNG/JPG/GIF/WebP·최대 2MB·권장 640px. 영상/음성 썸네일도 2MB(기존 20MB 아님)</t>
         </is>
       </c>
     </row>
@@ -52709,7 +52709,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">저장</t>
+          <t xml:space="preserve">검증</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -52719,17 +52719,17 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">입력 후 등록</t>
+          <t xml:space="preserve">썸네일 규격 초과·비허용</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draft 상태로 BIVE 관리 리스트 추가 + 토스트</t>
+          <t xml:space="preserve">썸네일 2MB 초과 또는 비허용 확장자 업로드 시 alert 후 등록 안 됨</t>
         </is>
       </c>
     </row>
@@ -52746,32 +52746,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">헤더</t>
+          <t xml:space="preserve">검증</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">상태확인</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태별 액션</t>
+          <t xml:space="preserve">썸네일 미등록 시 등록 비활성화</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draft=[삭제][저장][활성화] / Active=[비활성화](연결 캠페인 0·종료 시) / Inactive=[활성화]</t>
+          <t xml:space="preserve">이미지 타입 메인만 등록하고 썸네일 미등록 시 [등록] 버튼 비활성화(전 타입 썸네일 필수). 서브 이미지 미등록은 허용</t>
         </is>
       </c>
     </row>
@@ -52788,17 +52788,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기본정보 탭</t>
+          <t xml:space="preserve">기능설정 탭</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -52808,12 +52808,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기본정보·미디어·관리 정보</t>
+          <t xml:space="preserve">토글 3종</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명칭 read-only·미디어 타입별 미리보기·관리 정보 카드</t>
+          <t xml:space="preserve">보내기(Send)·Mix·Pick(기본 ON)</t>
         </is>
       </c>
     </row>
@@ -52830,32 +52830,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기능설정 탭</t>
+          <t xml:space="preserve">검증</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">에러 메시지 확인</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">토글 상태별 잠금</t>
+          <t xml:space="preserve">필수 누락 / 동일 조합 중복</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draft=수정 가능 / Active·Inactive=read-only</t>
+          <t xml:space="preserve">'설정되지 않은 정보가 있습니다.' / 동일 (아티스트·등급·등급번호) 중복 에러</t>
         </is>
       </c>
     </row>
@@ -52872,32 +52872,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">민팅관리 탭</t>
+          <t xml:space="preserve">저장</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 상세</t>
+          <t xml:space="preserve">BIVE 등록</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI확인</t>
+          <t xml:space="preserve">데이터입력</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">연결 캠페인</t>
+          <t xml:space="preserve">입력 후 등록</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태·유형·캠페인명(링크)·민팅횟수·연결일시, 캠페인명 클릭 시 민팅 상세 새 창</t>
+          <t xml:space="preserve">Draft 상태로 BIVE 관리 리스트 추가 + 토스트</t>
         </is>
       </c>
     </row>
@@ -52919,7 +52919,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">민팅이력 탭</t>
+          <t xml:space="preserve">헤더</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -52934,12 +52934,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">민팅 이력</t>
+          <t xml:space="preserve">상태별 액션</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">총 발행 + 검색(닉네임/지갑) + 테이블(Token ID·닉네임 링크·지갑 링크·민팅일시)</t>
+          <t xml:space="preserve">Draft=[삭제][저장][활성화] / Active=[비활성화](연결 캠페인 0·종료 시) / Inactive=[활성화]</t>
         </is>
       </c>
     </row>
@@ -52961,7 +52961,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">활성화</t>
+          <t xml:space="preserve">기본정보 탭</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -52971,17 +52971,17 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draft [활성화]</t>
+          <t xml:space="preserve">기본정보·미디어·관리 정보</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수 기본정보·미디어 저장이 완료된 상태에서만 Active 전환(미저장 시 '활성화 실패' 토스트)</t>
+          <t xml:space="preserve">명칭 read-only·미디어 타입별 미리보기·관리 정보 카드</t>
         </is>
       </c>
     </row>
@@ -53003,7 +53003,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비활성화</t>
+          <t xml:space="preserve">기본정보 탭</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -53013,17 +53013,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 민팅 관리에서 캠페인 연결([CEB-BO-BIVE 민팅 관리] 참조) — Active [비활성화]</t>
+          <t xml:space="preserve">이미지 타입 썸네일 미리보기</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">연결 캠페인 모두 종료 시 Inactive, 활성/중지 캠페인 존재 시 차단 토스트</t>
+          <t xml:space="preserve">이미지 타입 미디어 카드에 메인 이미지·서브 이미지·'썸네일 (저용량)' 3장 미리보기. 전 타입 썸네일 필수라 정상 데이터에서 항상 표시</t>
         </is>
       </c>
     </row>
@@ -53045,27 +53045,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 모달</t>
+          <t xml:space="preserve">기본정보 탭</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIVE 삭제</t>
+          <t xml:space="preserve">BIVE 상세</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">데이터입력</t>
+          <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draft [삭제]</t>
+          <t xml:space="preserve">도감·컬렉션 리스트 썸네일 로딩</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삭제 모달 → 확정 → BIVE 관리 복귀(Active·Inactive는 삭제 미노출)</t>
+          <t xml:space="preserve">도감([CEB-COL-101])·홈 BIVE 프리뷰([CEB-HOM-001]) 카드는 저용량 썸네일 사용(원본 직접 로딩 아님). 상세 미리보기만 원본 (앱 측 실측은 앱 QA 별도)</t>
         </is>
       </c>
     </row>
@@ -53082,30 +53082,282 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기능설정 탭</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">토글 상태별 잠금</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draft=수정 가능 / Active·Inactive=read-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_BVE_0031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에디션 관리</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민팅관리 탭</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연결 캠페인</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태·유형·캠페인명(링크)·민팅횟수·연결일시, 캠페인명 클릭 시 민팅 상세 새 창</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_BVE_0032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에디션 관리</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민팅이력 탭</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UI확인</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민팅 이력</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">총 발행 + 검색(닉네임/지갑) + 테이블(Token ID·닉네임 링크·지갑 링크·민팅일시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_BVE_0033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에디션 관리</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">활성화</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draft [활성화]</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">필수 기본정보·미디어 저장이 완료된 상태에서만 Active 전환(미저장 시 '활성화 실패' 토스트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_BVE_0034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에디션 관리</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비활성화</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태확인</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(사전조건) 민팅 관리에서 캠페인 연결([CEB-BO-BIVE 민팅 관리] 참조) — Active [비활성화]</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">연결 캠페인 모두 종료 시 Inactive, 활성/중지 캠페인 존재 시 차단 토스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_BVE_0035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에디션 관리</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 상세</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제 모달</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BIVE 삭제</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draft [삭제]</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삭제 모달 → 확정 → BIVE 관리 복귀(Active·Inactive는 삭제 미노출)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_BVE_0036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에디션 관리</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">앱 연동</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">연동</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">앱 BIVE</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">앱 연동 확인</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">민팅이력 회원·지갑 링크</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">닉네임→회원상세 / 지갑주소→BSCScan 새 창 (앱 측 실측은 본 시트 범위 외 — 앱 QA 별도)</t>
         </is>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -108,7 +108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -318,12 +318,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정렬 드롭다운</t>
+          <t xml:space="preserve">검색 대상 드롭다운</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가입일 최신순(기본)/오래된순/유저명</t>
+          <t xml:space="preserve">유저명/전화번호/지갑주소 (기본 유저명). 선택 대상 기준 키워드 부분 일치 검색 (BO: 정렬 드롭다운 없음)</t>
         </is>
       </c>
     </row>
@@ -365,7 +365,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">닉네임 부분 일치, 초기화 시 필터·검색 리셋</t>
+          <t xml:space="preserve">닉네임 부분 일치(BO 확인), 초기화 시 검색어·필터 리셋(BO 확인)</t>
         </is>
       </c>
     </row>
@@ -449,7 +449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">계정상태/유저명/전화번호(국가코드+번호)/지갑주소/가입일시</t>
+          <t xml:space="preserve">계정상태/유저명/전화번호(국가코드+번호)/지갑주소/가입일시. 유저명·지갑주소 셀에 [복사] 버튼</t>
         </is>
       </c>
     </row>
@@ -612,12 +612,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loading / 검색 0건 / 전체 0건</t>
+          <t xml:space="preserve">Loading / 결과 0건(검색·전체 공통)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skeleton / '검색 결과가 없습니다.' / '등록된 회원이 없습니다.'</t>
+          <t xml:space="preserve">Skeleton / 결과 없음 시 '조회된 회원이 없습니다.' (검색·전체 단일 메시지)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'회원 목록 조회에 실패하였습니다.' + [재시도]</t>
+          <t xml:space="preserve">'회원 목록 조회에 실패하였습니다.' + [재시도] (서버 에러 강제 불가 — 실측필요, 환경 제약)</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">탭 메뉴 9종</t>
+          <t xml:space="preserve">탭 메뉴 9종 + URL</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기본정보/참여내역/게임존/BIVE/프로젝트/Fans/티켓/지갑/활동내역 (URL ?tab=). 실구현 탭=기본정보·참여내역·게임존·BIVE, 준비중 탭=프로젝트·Fans·티켓·지갑·활동내역(진입 시 준비중 안내)</t>
+          <t xml:space="preserve">기본정보(basic)/참여내역(activity)/게임존(gamezone)/BIVE(bive)/프로젝트(project)/Fans(fans)/티켓(ticket)/지갑(wallet)/활동내역(log). 실구현=기본정보·참여내역·게임존·BIVE, 준비중=프로젝트·Fans·티켓·지갑·활동내역</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skeleton / '존재하지 않는 회원입니다.' 후 리스트 리다이렉트</t>
+          <t xml:space="preserve">Skeleton / 없는 ID 진입 시 '존재하지 않는 회원입니다.' (리스트 리다이렉트 여부 실측필요)</t>
         </is>
       </c>
     </row>
@@ -911,7 +911,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정상↔정지 전환(쓰기 권한 시). 토글 동작·계정상태 전환만 검증</t>
+          <t xml:space="preserve">계정정지 스위치 존재(클릭 가능). BO 실측: 토글 클릭에 상태 전환·확인 모달 동작 미재현 — 동작 실측필요(개발팀 확인)</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 신고 누적·반복 반려·다중계정·비정상 응모 등 트리거 데이터 주입. 트리거 충족 시 기본정보 탭에 '검토 필요' 배지 노출 (트리거 데이터 주입 불가 시 — 현 단계: 배지 노출 영역 존재 여부만 검증)</t>
+          <t xml:space="preserve">트리거 충족 시 기본정보 탭 '검토 필요' 배지 노출 (트리거 데이터 주입 불가 — 실측필요, 환경 제약)</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) 해당 데이터 보유 회원 검색(게임 참여 이력 계정/검색키). PM/ST 탭 + 게임상태·기간 필터 + 테이블(타이틀·아티스트·참여·선택·참여GP·부스팅GP·결과·보상GP·응모권·덕력·상태)</t>
+          <t xml:space="preserve">(사전조건) 게임 참여 이력 보유 회원. PM/ST 탭 + 게임상태·조회기간 필터 + 테이블(게임타이틀·참여일시·선택·참여GP·부스팅GP·게임결과·보상GP·환급GP·게임상태)</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">게임 참여 0건 / 휴면 안내</t>
+          <t xml:space="preserve">게임 참여 0건 / 게임존 데이터</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PM/ST 휴면 환경에서는 '현재 게임존(PM·ST)은 운영 중단 상태입니다.' 안내 표시</t>
+          <t xml:space="preserve">게임 참여 0건 시 Empty 안내. 테스트 BO는 PM 게임 진행중 데이터 존재 — '운영 중단' 안내는 게임 0건 환경에서만 노출</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) BIVE 보유 회원 검색(보유 이력 계정/검색키). 총 보유 수 + 등급 필터(전체/Event/Ticket/Mix/Pick) + 명칭 검색 + [초기화]</t>
+          <t xml:space="preserve">(사전조건) BIVE 보유 회원. 총 보유 수 + 등급 필터(등급(전체)/Event/Normal/Special/Wicked/Next/Final) + 명칭 검색 + [초기화]</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기본정보(에디션·아티스트 그룹·아티스트·등급·등급번호·민팅일시)·기능상태(보내기·Mix·PICK)·민팅정보(Token ID·이벤트·홀더·지갑)·BIVE 이미지</t>
+          <t xml:space="preserve">기본정보(에디션·아티스트 그룹·아티스트 3언어·등급·등급번호·민팅일시)·기능상태(보내기·Mix·PICK)·민팅정보(Token ID·민팅이벤트·홀더·홀더지갑)·BIVE 이미지</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태확인</t>
+          <t xml:space="preserve">UI확인</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'토큰 히스토리는 추후 제공됩니다.' 안내</t>
+          <t xml:space="preserve">토큰 히스토리 탭 — 트랜잭션 이력 테이블(트랜잭션 타입·TXID·보낸 유저·받은 유저·일시). 받기/보내기/상품 구매 등 (BO 실측: '추후 제공' 안내 아님, 실제 구현)</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태·코드(SUS_NNNN)·운영자 노출명·적용 가능 단계·사용 횟수·최근 사용일시·등록일시</t>
+          <t xml:space="preserve">상태·운영자 노출명·유저 노출 메시지(한국어)·유저 노출 메시지(영어)·유저 노출 메시지(일본어)·수정하기 (BO: 코드·적용 가능 단계·사용 횟수·최근 사용일시·등록일시 컬럼 없음)</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">등록일시 내림차순 / '등록된 정지사유가 없습니다…' / '해당 상태의 정지사유가 없습니다.'</t>
+          <t xml:space="preserve">정렬: 등록일시 내림차순(BO 실측 — 신규 사유 최상단 확인) / 검색·필터 0건 시 '검색 조건에 맞는 정지사유가 없습니다.'</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">추가 모달 — 운영자 노출명(20자) + 유저 노출 메시지 다국어(KO/EN/JA)</t>
+          <t xml:space="preserve">추가 모달 — 운영자 노출명(20자) + 유저 노출 메시지 다국어(한국어 기본값/영어/일본어, 각 200자). [취소하기]/[추가하기]</t>
         </is>
       </c>
     </row>
@@ -1994,12 +1994,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">운영자 노출명 또는 한국어 메시지 미입력</t>
+          <t xml:space="preserve">활성 조건</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[추가하기] 비활성</t>
+          <t xml:space="preserve">운영자 노출명 + 유저 노출 메시지 한국어/영어/일본어 3개 언어 모두 입력해야 [추가하기] 활성 (BO 실측: 한국어만으론 비활성)</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사유 등록(자동 '사용' 상태·코드 자동 채번) + 리스트 갱신</t>
+          <t xml:space="preserve">사유 등록(자동 '사용' 상태) + 리스트 최상단 추가(등록 최신순). 코드(SUS_) 미표기 — BO 실측 정합</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">수정 모달(기존값 prefill, 코드 read-only, 상태 변경 가능)</t>
+          <t xml:space="preserve">수정 모달(운영자 노출명·유저 노출 메시지 다국어 prefill, 상태 사용/미사용 변경 가능). BO: 코드 필드 없음</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,133 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">배지 회색 전환, 이후 제재 시 미노출(이력 보존, 삭제 없음)</t>
+          <t xml:space="preserve">미사용 전환·저장 시 배지 회색(사용=초록 배지). 제재 모달 미노출, 이력 보존(BO 실측 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_USR_0048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색·필터</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원 리스트</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">검색 대상 전환(유저명/전화번호/지갑주소) 후 검색</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택 대상 기준 부분 일치 결과. URL ?field= 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_USR_0049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">통계 카드</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원 리스트</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">버튼클릭</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상태 카드(정상/정지/탈퇴대기/탈퇴완료) 클릭</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해당 상태로 필터(URL ?status=). 정지 배지=빨강(흰 글자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC_USR_0050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회원</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정지사유 설정</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리스트</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정지사유 설정</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">데이터입력</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">운영자 노출명 검색 + [초기화]</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">노출명 부분 일치 필터, 초기화 시 리셋 (BO: 검색창·초기화 존재)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -48957,7 +48957,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/타이틀/아티스트/진행 방식/반복 주기/기간/검토 필요(7컬럼)</t>
+          <t xml:space="preserve">상태/타이틀/아티스트/기간/진행방식/반복주기/검토 필요 (7컬럼, BO 실측 순서: 기간이 진행방식·반복주기 앞)</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49125,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'팬퀘스트가 없습니다.' / Skeleton</t>
+          <t xml:space="preserve">'검색 결과가 없습니다.' / Skeleton (BO 실측: '팬퀘스트가 없습니다.' 아님)</t>
         </is>
       </c>
     </row>
@@ -49247,7 +49247,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아티스트·퀘스트 타입(이미지 촬영 및 업로드)·참여 방식(일반/반복)·마감 일시</t>
+          <t xml:space="preserve">아티스트·퀘스트 타입(이미지 촬영 및 업로드)·반복 참여(OFF/ON 토글)·마감 일시 (BO 실측: 참여 방식이 "반복 참여" OFF/ON 토글)</t>
         </is>
       </c>
     </row>
@@ -49373,7 +49373,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">응모권(장)·덕력(DUK)·NFT 체크박스+수량, 1개 이상 필수</t>
+          <t xml:space="preserve">보상 종류 드롭다운(응모권/덕력/NFT 중 선택) + 수량. BO 실측: 단일 선택 드롭다운(문서·QA의 3체크박스 다중선택 아님), 기본 응모권</t>
         </is>
       </c>
     </row>
@@ -49536,12 +49536,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">반복 주기 미선택 / 보상 0개</t>
+          <t xml:space="preserve">검증</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[생성하기] 비활성 + '보상 항목을 1개 이상 선택해주세요.'</t>
+          <t xml:space="preserve">다국어 일부 미입력 시 [생성하기] 비활성. 보상은 종류 드롭다운 단일 선택(기본 응모권 — "0개" 케이스는 드롭다운 구조상 미발생, 재검토필요)</t>
         </is>
       </c>
     </row>
@@ -49583,7 +49583,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성 완료 모달 → [확인] → 리스트 복귀, 임시저장 상태로 생성</t>
+          <t xml:space="preserve">생성 확인 모달("확인 버튼을 누르면 신규 Quest가 생성됩니다") → [확인] → 임시저장 상태로 생성 + 리스트 복귀 (BO 실측 확인)</t>
         </is>
       </c>
     </row>
@@ -49709,7 +49709,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">임시저장=[삭제][수정][게시] / 진행중=[수정][종료] / 종료=없음</t>
+          <t xml:space="preserve">임시저장=[삭제하기][수정하기][게시하기] / 진행중=[수정하기][종료하기] / 종료=없음 (BO 실측 확인)</t>
         </is>
       </c>
     </row>
@@ -49919,7 +49919,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">매핑 0건='아직 매핑되지 않았습니다' / N건=그룹·에피소드·미션 목록, 행 클릭 시 미션 상세 이동</t>
+          <t xml:space="preserve">매핑 0건='아직 매핑되지 않았습니다' / N건=그룹·에피소드·퀘스트(CHAPTER)·바로가기 목록 (BO 용어: 퀘스트(CHAPTER))</t>
         </is>
       </c>
     </row>
@@ -50003,7 +50003,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'진행중 상태로 게시됩니다' 모달 → [확인] → 진행중 전환 + 토스트 + 시작일시 자동 기록</t>
+          <t xml:space="preserve">임시저장 [게시하기] → "Quest 게시 / 확인 버튼을 누르면 Quest가 게시됩니다" 모달 [취소][게시] → [게시] → 진행중 전환 (BO 실측: 문구가 "진행중 상태로 게시됩니다" 아님)</t>
         </is>
       </c>
     </row>
@@ -50129,7 +50129,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'복구할 수 없습니다'(위험 톤) 모달, 매핑 미션 자동 해제 안내 → [삭제] → 리스트 복귀</t>
+          <t xml:space="preserve">임시저장 [삭제하기] → "Quest 삭제 / 확인 버튼을 누르면 Quest가 삭제 됩니다" 모달 [취소][삭제] → [삭제] → 리스트 복귀 (BO 실측: "복구할 수 없습니다" 위험 톤·매핑 해제 안내 문구 없음)</t>
         </is>
       </c>
     </row>
@@ -50171,7 +50171,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">버튼 미노출(임시저장만 가능)</t>
+          <t xml:space="preserve">진행중·종료 상세에는 [삭제하기] 미노출(임시저장만 삭제 가능) — BO 실측 확인</t>
         </is>
       </c>
     </row>
@@ -50751,7 +50751,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">페이지당 10건 / '검수할 제출이 없습니다.'(액션 바·페이지네이션 미노출)</t>
+          <t xml:space="preserve">페이지당 10건 / 검수 대기 0건 시 '제출내역이 없습니다.' (BO 실측: '검수할 제출이 없습니다.' 아님). 검수 액션은 제출 데이터 필요 — 실측필요</t>
         </is>
       </c>
     </row>
@@ -51037,7 +51037,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/제출ID/유저닉네임/반려사유/이미지(확대)/제출일시/처리일시/처리자(8컬럼)</t>
+          <t xml:space="preserve">상태/제출ID/유저닉네임/반려사유/이미지(확대)/제출일시/처리일시/처리자(8컬럼) — 처리 데이터 0건이라 컬럼 실측필요(데이터 필요)</t>
         </is>
       </c>
     </row>
@@ -51243,7 +51243,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">운영자 노출명(100자, 필수) + 유저 노출 메시지 다국어(KO 필수/EN·JA 선택)</t>
+          <t xml:space="preserve">운영자 노출명(100자, 필수) + 유저 노출 메시지 다국어(한국어/영어/일본어). BO 실측: 운영자 노출명 100자 ✓</t>
         </is>
       </c>
     </row>
@@ -51280,12 +51280,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">운영자 노출명 또는 한국어 메시지 미입력</t>
+          <t xml:space="preserve">활성 조건</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[추가하기] 비활성</t>
+          <t xml:space="preserve">운영자 노출명 + 유저 노출 메시지 한국어/영어/일본어 3개 언어 모두 입력해야 [추가하기] 활성 (BO 실측: KO만으론 비활성 — 문서·QA "KO 필수/EN·JA 선택"과 다름)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -52351,7 +52351,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">기존값 prefill, 'BIVE 등록·민팅 시 명칭 수정 불가' 안내</t>
+          <t xml:space="preserve">기존값 prefill, 'BIVE를 등록 후 통합 관리합니다. 에디션 명칭은 등록된 BIVE가 없을때 수정이 가능합니다.' 안내. 수정 모달에 삭제 기능 없음(수정하기만) — BO 실측</t>
         </is>
       </c>
     </row>
@@ -52393,7 +52393,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">명칭 입력 read-only + [수정하기] 비활성(BIVE 0·민팅 0일 때만 수정 가능)</t>
+          <t xml:space="preserve">BIVE 1개 이상/민팅 발생 에디션은 [수정하기] 비활성(BIVE 0·민팅 0일 때만 수정). BO 실측: 입력 필드는 편집 가능하나 저장(수정하기)만 차단 — literally read-only 아님</t>
         </is>
       </c>
     </row>
@@ -52729,7 +52729,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지(메인 이미지 필수+서브 이미지 선택+썸네일 필수)/영상(MP4 50MB+썸네일 필수)/음성(MP3 10MB+썸네일 필수), 타입 변경 시 기존 파일 초기화</t>
+          <t xml:space="preserve">이미지(메인★+서브 선택+썸네일★)/영상(MP4 50MB+썸네일★)/음성(MP3 10MB+썸네일★). BO 실측: 이미지 확장자 png/jpg/jpeg/webp(GIF 미지원), PNG·JPG는 크롭 후 WebP 자동 저장. 타입 변경 시 기존 파일 초기화</t>
         </is>
       </c>
     </row>
@@ -52771,7 +52771,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이미지 타입 선택 시 메인 이미지·서브 이미지 grid 아래 '썸네일 ★' 박스 노출. 안내 'PNG/JPG/GIF/WebP · 최대 2MB · 권장 가로 640px · WebP 우선'</t>
+          <t xml:space="preserve">이미지 타입 선택 시 메인·서브 grid 아래 '썸네일 ★' 박스 노출. 안내 'PNG/JPG/WebP'(GIF 미지원). 썸네일 저용량 2MB·640px는 개발 예정 — 현재 BO 안내는 최대 20MB</t>
         </is>
       </c>
     </row>
@@ -52813,7 +52813,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전 미디어 타입(이미지·영상·음성) 썸네일 동일 규격 — PNG/JPG/GIF/WebP·최대 2MB·권장 640px. 영상/음성 썸네일도 2MB(기존 20MB 아님)</t>
+          <t xml:space="preserve">썸네일 저용량 규격(PNG/JPG/WebP·최대 2MB·권장 640px)은 개발 예정 스펙. BO 실측 현재: 메인·서브·썸네일 모두 png/jpg/jpeg/webp·최대 20MB(저용량 미구현) — 🟡 BO 미반영</t>
         </is>
       </c>
     </row>
@@ -52855,7 +52855,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">썸네일 2MB 초과 또는 비허용 확장자 업로드 시 alert 후 등록 안 됨</t>
+          <t xml:space="preserve">썸네일 2MB 초과 또는 비허용 확장자(GIF 등) 업로드 시 alert 후 등록 안 됨 (저용량 2MB 검증은 개발 예정, 현재 BO 20MB)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -53711,7 +53711,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태 배지·보상방식 배지(가중치/지정)·캠페인명·연결 기능·등록 BIVE 수·발행 수·생성일</t>
+          <t xml:space="preserve">ID·상태 배지·캠페인 명·연결 기능·보상 선택(가중치/고정)·등록된 BIVE 수·발행 수·생성일 (BO 실측: ID 컬럼 포함, 보상방식 리스트·관리정보="고정" / BIVE 보상 탭 라디오="지정 보상"으로 혼용)</t>
         </is>
       </c>
     </row>
@@ -53879,7 +53879,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">캠페인명(2~30자) + 연결 기능 7종(회원가입·출석체크·래플·팬퀘스트·에피소드·덕력랭킹·아티스트 키우기 보상)</t>
+          <t xml:space="preserve">캠페인명(placeholder "캠페인 명을 입력하세요") + 연결 기능 7종(회원가입 보상·출석체크 보상·래플 보상·팬퀘스트 보상·에피소드 보상·덕력 시즌 보상·아티스트 키우기 보상). BO 실측: "덕력랭킹" 아닌 "덕력 시즌 보상"</t>
         </is>
       </c>
     </row>
@@ -54257,7 +54257,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">초안=[삭제][저장][활성화] / 활성=[일시중지] / 중지=[저장][활성화] / 종료=없음</t>
+          <t xml:space="preserve">초안=[삭제][저장][활성화] / 활성=[일시중지] / 중지=[저장][활성화] / 종료=없음 (BO 실측: 활성 상세 헤더 [일시중지] 확인)</t>
         </is>
       </c>
     </row>
@@ -55239,7 +55239,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'등록된 혜택이 없습니다.' / '조건에 맞는 혜택이 없습니다.'</t>
+          <t xml:space="preserve">'검색 결과가 없습니다.' (BO 실측 — 단일 메시지, QA '등록된 혜택이 없습니다.'/'조건에 맞는…' 아님)</t>
         </is>
       </c>
     </row>
@@ -55281,7 +55281,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">혜택 생성(2탭: 기본정보/BIVE 추가) 진입, 타이틀 '{유형} 혜택 생성'</t>
+          <t xml:space="preserve">혜택 생성(2탭: 기본정보/BIVE 추가) 진입, 타이틀 "Boost point 혜택 생성"(유형별) — BO 실측 정합</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -4265,7 +4265,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">페이지당 20건 / '래플이 없습니다.'</t>
+          <t xml:space="preserve">페이지당 10건 / '검색 결과가 없습니다.' (BO 실측: QA '20건'·'래플이 없습니다.' 아님)</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">(사전조건) raffle 음성/양성 테스트 페어 등 상태별 데이터(임시저장·진행중·추첨대기 응모 0건·추첨대기 응모 1건↑) 준비. 임시저장·진행중='추첨대기일 때만 가능' / 추첨대기+응모 0건='자동 종료·입상자 없음' / 추첨대기+응모 1건↑=[추첨하기]</t>
+          <t xml:space="preserve">임시저장·진행중=추첨 불가 안내 / 추첨대기='추첨대기 상태에서는 하단 추첨하기 버튼을 눌러 추첨을 진행해주세요' + [추첨하기]. BO 실측: 추첨대기는 응모 0건이어도 [추첨하기] 노출(QA '0건=자동 종료·입상자 없음'과 다름 — 재확인필요)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -4307,7 +4307,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">래플 생성 진입(좌: 래플 정보 / 중: 보상 / 우: 수령 가이드)</t>
+          <t xml:space="preserve">Raffle 생성 진입 — 3섹션(Raffle 정보 / 보상 기본 설정 / 수령 가이드 및 유의사항). BO 실측 정합</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">배송 수령=배송지 입력 마감일시·폼 URL / 현장 수령=수령 시작/마감일·운영 시간·수령 장소(다국어)·지참물(다국어)</t>
+          <t xml:space="preserve">배송 수령=배송지 입력 마감일·마감 시간·폼 URL / 현장 수령=수령 시작일·마감일·운영 시작/마감 시간·수령 장소·지참물(다국어). BO 실측 정합</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">임시저장·진행중=추첨 불가 안내 / 추첨대기='추첨대기 상태에서는 하단 추첨하기 버튼을 눌러 추첨을 진행해주세요' + [추첨하기]. BO 실측: 추첨대기는 응모 0건이어도 [추첨하기] 노출(QA '0건=자동 종료·입상자 없음'과 다름 — 재확인필요)</t>
+          <t xml:space="preserve">임시저장·진행중=추첨 불가 안내 / 추첨대기='하단 추첨하기 버튼으로 추첨 진행' + [추첨하기]. BO 실측: 추첨대기는 응모 0건이어도 [추첨하기] 노출, 클릭 시 '응모자가 없어 추첨할 대상이 없습니다.' 안내(QA '0건=자동 종료·입상자 없음'과 다름)</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가추첨 시드·가중치 기반 추첨(응모권 수 정비례)·재추첨(무제한)·당첨자 미리보기(10건 페이지) → [추첨 확정]</t>
+          <t xml:space="preserve">추첨 모달 'Raffle 추첨하기'+'추첨 정보'. 응모 0건=‘응모자가 없어 추첨할 대상이 없습니다.’+[닫기]. 가추첨 시드·당첨자 미리보기·재추첨·[추첨 확정] UI는 응모자 보유 raffle 필요 — 실측필요(데이터, 추첨 확정은 되돌리기 불가라 미실행)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -6313,7 +6313,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">응모권 변동내역 진입</t>
+          <t xml:space="preserve">변동 내역 진입(BO 타이틀 "변동 내역")</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">응모권 관리(정책) 진입 + '1일 기준 KST 자정' 안내</t>
+          <t xml:space="preserve">응모권 발급 정책 진입(BO h1 "응모권 발급 정책") + "1일 기준: KST 자정(00:00~23:59:59), 매일 자정 회원별 한도 자동 리셋" 안내</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -16735,7 +16735,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/그룹명/멤버 수/팔로워 수/탐색 노출/업데이트 일시</t>
+          <t xml:space="preserve">상태/그룹명/멤버 수/설명/업데이트 일시 (BO 실측: 팔로워 수·탐색 노출 컬럼 없음, 설명 컬럼 존재)</t>
         </is>
       </c>
     </row>
@@ -16777,7 +16777,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태 배지·그룹명(한국어)·멤버 수·팔로워 수(천단위 콤마)·업데이트 일시(YYYY.MM.DD HH:mm)</t>
+          <t xml:space="preserve">상태 배지(Active=teal/Inactive)·그룹명(한국어)·멤버 수·설명·업데이트 일시(YYYY.MM.DD HH:mm)</t>
         </is>
       </c>
     </row>
@@ -16819,7 +16819,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">행별 켬/끔 토글 스위치 표시</t>
+          <t xml:space="preserve">BO 실측: 리스트 행에 켬/끔 토글 스위치 없음(상태는 배지). 탐색 노출 토글은 리스트 테이블에 미존재 — 재확인필요</t>
         </is>
       </c>
     </row>
@@ -16861,7 +16861,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">즉시 켬/끔 변경 + "'{그룹명}'의 탐색 노출을 켬/끔으로 변경했습니다" 토스트</t>
+          <t xml:space="preserve">BO 실측: 리스트 행 토글 미존재 — 해당 토글/토스트 동작 BO 미반영(상세 화면 여부 재확인)</t>
         </is>
       </c>
     </row>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">페이지당 10건, 하단 중앙</t>
+          <t xml:space="preserve">페이지당 15건, 하단 중앙 (BO 실측: 전체 18건=15+3, QA "10건" 아님)</t>
         </is>
       </c>
     </row>
@@ -17071,7 +17071,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'등록된 그룹이 없습니다.' 메시지</t>
+          <t xml:space="preserve">'검색 결과가 없습니다.' (BO 실측 — 단일 메시지)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -18349,7 +18349,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1 권장 512×512px, 최대 5MB 안내</t>
+          <t xml:space="preserve">로고(심볼) — 권장 512×512px(1:1)·jpeg/png/jpg/webp/gif/svg·최대 5MB (BO 실측)</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16:9 권장 1920×1080px, 최대 5MB 안내</t>
+          <t xml:space="preserve">대표이미지(배너) — 권장 1920×1080px(16:9)·jpeg/png/jpg/webp/gif/svg·최대 5MB (BO 실측)</t>
         </is>
       </c>
     </row>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'지원하지 않는 형식입니다. (JPG·PNG·WebP)' 에러</t>
+          <t xml:space="preserve">지원하지 않는 형식 업로드 시 에러. BO 실측: 허용 형식 = jpeg/png/jpg/webp/gif/svg (QA "JPG·PNG·WebP만"과 다름 — gif·svg도 허용)</t>
         </is>
       </c>
     </row>
@@ -18979,7 +18979,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성 완료 모달, 제목 '그룹 생성' + '확인 버튼을 누르면 그룹이 생성됩니다 / 계속 진행하시겠습니까?'</t>
+          <t xml:space="preserve">생성 완료 모달 '그룹 생성' + '확인 버튼을 누르면 그룹이 생성됩니다 / 계속 진행하시겠습니까?' (그룹 삭제 불가로 실제 생성 미실행 — 모달 텍스트 기준)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -19395,7 +19395,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">운영 상태 배지·로고 등록됨/미등록·팔로워 수·생성자/생성일시·수정자/수정일시</t>
+          <t xml:space="preserve">운영 상태 배지(Active/Inactive)·로고 등록됨/미등록·운영 상태(노출 중/숨김)·생성자/생성일시·수정자/수정일시 (BO 실측: 팔로워 수 미표시 — 리스트·상세 모두 BO에 팔로워 수 없음)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -19769,7 +19769,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[취소하기]·[수정하기] + 로고·배너는 기존 이미지 + [변경]만(제거 없음)</t>
+          <t xml:space="preserve">[취소하기]·[수정하기] + 로고·배너는 기존 이미지 + [변경] 및 [제거] 버튼 (BO 실측: QA "제거 없음"과 다름 — [제거] 버튼 존재)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -21753,7 +21753,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skeleton / '등록된 멤버가 없습니다.' / '검색 결과가 없습니다.'</t>
+          <t xml:space="preserve">Skeleton / '검색 결과가 없습니다.' (BO 실측 — 단일 메시지)</t>
         </is>
       </c>
     </row>
@@ -22447,7 +22447,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1:1 비율, JPG·PNG·WebP, 최대 5MB</t>
+          <t xml:space="preserve">프로필 이미지 1:1 비율 · jpeg/png/jpg/webp/gif/svg · 최대 5MB (BO 실측: gif·svg도 허용)</t>
         </is>
       </c>
     </row>
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'지원하지 않는 형식입니다. (JPG·PNG·WebP)' 에러</t>
+          <t xml:space="preserve">지원하지 않는 형식 업로드 시 에러. BO 실측 허용 = jpeg/png/jpg/webp/gif/svg (QA "JPG·PNG·WebP"와 다름)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -37095,7 +37095,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'아티스트 그룹별 자동 적립 활동 덕력 지급량 설정, Quest·게임은 콘텐츠 직접 입력' 안내 + 그룹 드롭다운 + [권장값 적용]·[저장]</t>
+          <t xml:space="preserve">'아티스트 그룹별 자동 적립 활동의 덕력 지급량을 설정합니다.' 안내 + 그룹 드롭다운 + [권장값 적용]·[저장]</t>
         </is>
       </c>
     </row>
@@ -37179,7 +37179,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석 체크·응모권 사용·일일 미션·SNS 공유(기억 공유)·기억저장소 업로드·디지털 굿즈 획득(등급별 Normal/Event/Special/Wicked/Next/Final 6)·스트릭 7/14/21/28(자동 적립). Quest 완료·게임 참여는 제외(콘텐츠 직접 입력)</t>
+          <t xml:space="preserve">출석 체크·응모권 사용(1장당)·일일 미션 모두 완료·프리딕션 마켓 참여·트리비아 참여·SNS 공유(기억 공유)·에피소드 완료·팬퀘스트 완료·기억저장소 업로드·디지털 굿즈 획득(등급별 Normal/Event/Special/Wicked/Next/Final 6)·스트릭 7/14/21/28 (자동 적립 19개 행). 게임 참여·에피소드·팬퀘스트도 매트릭스 포함 [문서-BO 차이: 래플 응모는 BO 지급주기 '행동마다'로 1장당 미반영, 디지털 굿즈는 BO 단일 75로 6등급 미반영 — 개발 예정]</t>
         </is>
       </c>
     </row>
@@ -37515,7 +37515,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 아티스트 생성 시 권장값 기본 정책 자동 생성·사용 ON → '미설정' 상태 부재(항상 9개 활동 행 노출)</t>
+          <t xml:space="preserve">신규 아티스트 생성 시 권장값 기본 정책 자동 생성·사용 ON → '미설정' 상태 부재(항상 19개 활동 행 노출)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -37095,7 +37095,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'아티스트 그룹별 자동 적립 활동의 덕력 지급량을 설정합니다.' 안내 + 그룹 드롭다운 + [권장값 적용]·[저장]</t>
+          <t xml:space="preserve">'표의 값은 활동별 덕력 기본값입니다. 생성 화면에서 지급 덕력을 따로 입력하는 서비스는 입력한 값이 우선 지급됩니다. 별도 입력 폼이 없는 활동은 이 정책 값이 지급되며 사용 안함 시 미지급' 안내 + 그룹 드롭다운 + [권장값 적용]·[저장]</t>
         </is>
       </c>
     </row>
@@ -37179,7 +37179,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">출석 체크·응모권 사용(1장당)·일일 미션 모두 완료·프리딕션 마켓 참여·트리비아 참여·SNS 공유(기억 공유)·에피소드 완료·팬퀘스트 완료·기억저장소 업로드·디지털 굿즈 획득(등급별 Normal/Event/Special/Wicked/Next/Final 6)·스트릭 7/14/21/28 (자동 적립 19개 행). 게임 참여·에피소드·팬퀘스트도 매트릭스 포함 [문서-BO 차이: 래플 응모는 BO 지급주기 '행동마다'로 1장당 미반영, 디지털 굿즈는 BO 단일 75로 6등급 미반영 — 개발 예정]</t>
+          <t xml:space="preserve">출석 체크·응모권 사용(1장당)·일일 미션 모두 완료·프리딕션 마켓 참여·트리비아 참여·SNS 공유(기억 공유)·에피소드 완료·팬퀘스트 완료·기억저장소 업로드·디지털 굿즈 획득(등급별 6)·스트릭 7/14/21/28 (자동 적립 19개 행). 매트릭스 값=기본값: 입력 필드 있는 콘텐츠(팬퀘스트·게임·에피소드)는 생성 시 prefill 후 콘텐츠 입력값 우선, 입력 필드 없는 활동은 정책 값 직접 지급 [문서-BO 차이: 래플 응모는 BO '행동마다'로 1장당 미반영, 디지털 굿즈는 BO 단일 75로 6등급 미반영 — 개발 예정]</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -35905,7 +35905,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">모달 진입, 제목 '시즌을 강제 종료하시겠습니까?'</t>
+          <t xml:space="preserve">모달 진입, 제목 '덕력 시즌을 강제 종료할까요?' (BO 실측 — QA '시즌을 강제 종료하시겠습니까?'와 표기 차이)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -36737,7 +36737,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미정산='아직 정산되지 않았습니다(말일 23:59 자동 정산)' / 강제 종료='강제 종료된 시즌으로 지급 내역이 없습니다'</t>
+          <t xml:space="preserve">미정산='정산 완료된 보상 지급 내역이 없습니다.'(BO 실측) / 강제 종료='강제 종료된 시즌으로 지급 내역이 없습니다'</t>
         </is>
       </c>
     </row>
@@ -36813,7 +36813,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">순위/회원/등수 기준(아이콘+대상명)/상품 종류/상품명/지급 일시/지급 상태/액션</t>
+          <t xml:space="preserve">순위/회원/등수 기준(아이콘+대상명)/상품 종류/상품명/지급 일시/지급 상태/메모 (BO 실측 — QA 마지막 컬럼 '액션'→'메모')</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -28547,7 +28547,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/그룹/현재 시즌/시즌 기간/레벨 수/현재 팬덤 레벨/누적 덕력/참여 팬 수/업데이트 일시</t>
+          <t xml:space="preserve">상태/그룹/현재 시즌/시즌 기간/레벨 수/현재 레벨/누적 덕력/참여 팬 수/업데이트 일시/관리 (BO 실측 — QA "현재 팬덤 레벨"→"현재 레벨", 관리 컬럼 추가)</t>
         </is>
       </c>
     </row>
@@ -28799,7 +28799,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skeleton / '생성된 팬덤레벨이 없습니다.' / '검색 결과가 없습니다.'</t>
+          <t xml:space="preserve">Skeleton / '검색 결과가 없습니다.' (BO 실측 — 단일 메시지)</t>
         </is>
       </c>
     </row>
@@ -29555,7 +29555,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">레벨/레벨업 목표 덕력/권장값/레벨업 여부/레벨업 일시</t>
+          <t xml:space="preserve">레벨/레벨업 목표 덕력/권장값/달성 여부/달성 일시 (BO 실측 — QA "레벨업 여부/일시"→"달성 여부/일시")</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -31235,7 +31235,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">레벨/레벨업 일시/연결 보상, 레벨업 일시 내림차순</t>
+          <t xml:space="preserve">레벨/달성 일시/연결 보상, 달성 일시 내림차순 (BO 실측 — QA "레벨업 일시"→"달성 일시")</t>
         </is>
       </c>
     </row>
@@ -31319,7 +31319,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">회원/레벨/캠페인/지급 상태/일시</t>
+          <t xml:space="preserve">회원/레벨/보상명/지급 상태/일시 (BO 실측 — QA "캠페인"→"보상명")</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -39355,7 +39355,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">그룹 드롭다운(활성) + 목표 응원량(1 이상 정수, 덕력)</t>
+          <t xml:space="preserve">그룹 드롭다운(활성) + 목표 덕력(1 이상 정수) (BO 실측 — QA "목표 응원량"→"목표 덕력")</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -39149,7 +39149,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">회원/이벤트명/그룹/변동 내용(응원 +emerald, 반환 −rose)/일시, 회차별 1행</t>
+          <t xml:space="preserve">회원/이벤트명/그룹/응원량(응원 탭)·반환량(반환 탭)/일시, 회차별 1행 (BO 실측 — QA "변동 내용"→탭별 "응원량/반환량")</t>
         </is>
       </c>
     </row>
@@ -41157,7 +41157,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">닉네임/누적 응원량/응원 횟수(2회↑ 강조)/최초 응원/최근 응원/반환 여부, 누적 응원량 내림차순</t>
+          <t xml:space="preserve">유저명/누적 응원량/응원 횟수(2회↑ 강조)/최초 응원/최근 응원/반환 여부, 누적 응원량 내림차순 (BO 실측 — QA "닉네임"→"유저명")</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -24967,7 +24967,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/타입/제목/그룹/공식/일시</t>
+          <t xml:space="preserve">상태/타입/그룹/제목/일시/공식 여부/최근 수정 (BO 실측 — QA 6컬럼에 "최근 수정" 추가, "공식"→"공식 여부")</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -56657,7 +56657,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">타이틀·아티스트·상태 배지·참여자 수·총 상금 GP·참여기간·생성일·관리자</t>
+          <t xml:space="preserve">타이틀·상태 배지·참여자 수·총 상금 GP·참여기간·생성일·관리자 (BO 실측 PM 리스트 — QA "아티스트" 컬럼은 BO 리스트에 미표시)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -9275,7 +9275,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">관리자 리스트 진입(SUPER 전용)</t>
+          <t xml:space="preserve">관리자 리스트 진입(SUPER 전용), 타이틀 "관리자현황" (BO 실측 — QA "관리자 리스트")</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">권한 그룹 리스트 진입(SUPER 전용)</t>
+          <t xml:space="preserve">권한 그룹 리스트 진입(SUPER 전용), 타이틀 "권한관리" (BO 실측 — QA "권한 그룹 리스트")</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -42509,7 +42509,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/아티스트/타이틀/에피소드 수/시작일/종료일/최근 수정자</t>
+          <t xml:space="preserve">상태/아티스트/타이틀/시작일/종료일/최근 수정자/관리 (BO 실측 — QA "에피소드 수" 컬럼은 BO 리스트에 미표시, 마지막 관리 컬럼 존재)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -43387,7 +43387,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에피소드 상세(/sq/{id})로 이동</t>
+          <t xml:space="preserve">에피소드 상세(/sq/groups/{gid}/episodes/{id})로 이동 (BO 실측 — QA "/sq/{id}" 경로 정정)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -13369,7 +13369,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정수 유효성 안내 + [변경사항 저장] 비활성</t>
+          <t xml:space="preserve">정수 유효성 안내 + [일일미션 설정 저장] 비활성 (BO 실측 라벨)</t>
         </is>
       </c>
     </row>
@@ -13411,7 +13411,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효성 안내 + [변경사항 저장] 비활성</t>
+          <t xml:space="preserve">유효성 안내 + [일일미션 설정 저장] 비활성 (BO 실측 라벨)</t>
         </is>
       </c>
     </row>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">유효성 안내 + [변경사항 저장] 비활성</t>
+          <t xml:space="preserve">유효성 안내 + [일일미션 설정 저장] 비활성 (BO 실측 라벨)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -46631,7 +46631,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/타이틀/아티스트/진행 방식(일반·반복)/반복 주기/검토 필요(대기 건수 강조)</t>
+          <t xml:space="preserve">상태/타이틀/아티스트/기간/진행방식/반복주기/검토 필요(대기 건수 강조)/관리 (BO 실측 — QA에 "기간" 컬럼 추가)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -44799,7 +44799,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">미션 추가(/quests/create) 진입</t>
+          <t xml:space="preserve">미션 추가(/sq/groups/{gid}/episodes/{eid}/missions/create) 진입, h1 "새 미션 추가 (N/10)" (BO 실측 — QA "/quests/create" 경로 정정)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -40573,7 +40573,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'강제 종료할까요? 응원 회원 N명에게 N 덕력 전액 반환 / 되돌릴 수 없습니다' 모달({N} 스냅샷)</t>
+          <t xml:space="preserve">'서포트 모집을 강제 종료할까요?' 모달 + '모집이 종료되고 응원 덕력은 반환 대상으로 처리됩니다.' + 응원자 수 표시 (BO 실측 — QA 'N명에게 N덕력 전액 반환/되돌릴 수 없음'보다 BO 문구 간결)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -42715,7 +42715,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아티스트(필수)·상태(임시저장 기본/진행중/종료)·타이틀(80자)·시작/종료일자</t>
+          <t xml:space="preserve">아티스트(필수 드롭다운)·타이틀·시작일시·종료일시(달력 위젯+시간) (BO 실측 — 상태 선택 필드는 생성 폼에 없음(임시저장 기본 생성)·"일시" 단위(QA "일자"))</t>
         </is>
       </c>
     </row>
@@ -42757,7 +42757,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'진행중 상태는 아티스트당 1개만 허용' 안내</t>
+          <t xml:space="preserve">안내 'ACTIVE 상태는 아티스트당 1개만 허용됩니다.' (BO 실측 — 🟠 영문 enum 'ACTIVE' 노출, QA '진행중'. 기획자 언어로는 '진행중')</t>
         </is>
       </c>
     </row>
@@ -43009,7 +43009,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'변경사항을 저장하지 않으시겠습니까?' 확인 모달</t>
+          <t xml:space="preserve">네이티브 확인 '저장하지 않은 변경사항이 있습니다. 이동할까요?' (BO 실측 — QA '변경사항을 저장하지 않으시겠습니까?'와 문구 차이, 브라우저 confirm 사용)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -31487,7 +31487,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'팬덤레벨을 게시할까요? / 레벨 5개 이상' 모달 → 진행중 전환 + 토스트 + 헤더 갱신([강제 종료] 노출)</t>
+          <t xml:space="preserve">'팬덤레벨을 게시할까요? · 레벨 5개 이상' 모달 → 진행중 전환 + '{시즌명} 상태를 진행중(으)로 변경했습니다.' 토스트 + 헤더 [강제 종료][수정] 노출 (BO 실측 — QA 토스트 '게시했습니다'와 문구 차이)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -29345,7 +29345,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">준비=[삭제]·[게시] / 진행중=[강제 종료] / 종료=버튼 없음(쓰기 권한 시)</t>
+          <t xml:space="preserve">준비=[삭제]·[게시] / 진행중=[강제 종료]·[수정] / 종료=[수정] 비활성(쓰기 권한 시) (BO 실측 — QA '종료=버튼 없음'이나 실제는 수정 버튼 비활성 존재)</t>
         </is>
       </c>
     </row>
@@ -31865,7 +31865,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">'시즌을 강제 종료할까요? / 종료 후 수정 불가' 모달 → 종료 전환 + 토스트 + 헤더 갱신(곡선·보상 [수정] 비활성)</t>
+          <t xml:space="preserve">'시즌을 강제 종료할까요?' 모달 → 종료 전환 + '{시즌명} 상태를 종료(으)로 변경했습니다.' 토스트 + 헤더 [수정] 비활성(종료 후 수정 불가) (BO 실측)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -37137,7 +37137,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">활동·티어 배지·권장값(읽기 전용)·지급 덕력(입력)·사용 여부 토글</t>
+          <t xml:space="preserve">활동·티어 배지·지급 주기(읽기 전용)·권장값(읽기 전용)·지급 덕력(입력)·사용 여부 토글 (BO 6컬럼: 활동·등급·지급 주기·권장값·지급 덕력·사용 여부)</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -47387,7 +47387,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">전역 / 아티스트 팬덤(드롭다운) / 특정 회원 그룹(검색·CSV, 인원수 표시·탈퇴/휴면/차단 제외)</t>
+          <t xml:space="preserve">[수동 작성] 대상 섹션 — 카테고리(공통·필수, 4종: 아티스트/이벤트/게임존/공지) + 전역 / 아티스트 팬덤(드롭다운) / 특정 회원 그룹(CSV 파일 첨부만·이메일 매칭). 회원 그룹 첨부 후 하단 명단(번호·닉네임·이메일·페이지당 20명·총 회원 수)·탈퇴/휴면/차단 제외</t>
         </is>
       </c>
     </row>
@@ -47471,7 +47471,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">제목·본문 6필드+대상 미충족 시 토스트+누락 강조</t>
+          <t xml:space="preserve">[수동 작성] 제목·본문 6필드+카테고리(필수)+대상 미충족(회원 그룹은 CSV 미첨부) 시 [발송]/[예약] 차단·토스트+누락 강조</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -47009,7 +47009,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">대상(전역/팬덤/회원그룹)·채널(기본만/기본+푸시)·상태(6종)·키워드(제목)·[초기화]</t>
+          <t xml:space="preserve">[리스트] 카테고리(전체/아티스트/이벤트/게임존/공지)·대상(전역/팬덤/회원그룹)·채널(기본만/기본+푸시)·상태(6종)·키워드(제목)·[초기화]</t>
         </is>
       </c>
     </row>
@@ -47051,7 +47051,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">상태/채널/제목(KO)+본문 미리보기/대상/발송 시점/도달 수/작성자</t>
+          <t xml:space="preserve">[리스트] 상태/카테고리 배지/채널/제목(KO)+본문 미리보기/대상/발송 시점/도달 수/작성자</t>
         </is>
       </c>
     </row>

--- a/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
+++ b/v2/BO/00-Common/CELEBUS BO 단위테스트 v1.0.xlsx
@@ -48017,7 +48017,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">카테고리(래플/응원·퀘스트/BIVE/회원활동/시스템공지)·활성(사용중/미사용)·키워드 + 테이블(활성/카테고리/채널/트리거/제목/최근 발송)</t>
+          <t xml:space="preserve">[자동 트리거 탭] 카테고리(전체/아티스트/이벤트/게임존/공지 — 수동 알림과 동일 4종)·활성(사용중/미사용)·키워드 + 테이블(활성/카테고리/채널/트리거/제목/최근 발송)</t>
         </is>
       </c>
     </row>
